--- a/output/version3/test/25-15/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1278</v>
       </c>
       <c r="C2" t="n">
-        <v>1303</v>
+        <v>1168</v>
       </c>
       <c r="D2" t="n">
-        <v>1261</v>
+        <v>1146</v>
       </c>
       <c r="E2" t="n">
-        <v>1416</v>
+        <v>1173</v>
       </c>
       <c r="F2" t="n">
-        <v>1060</v>
+        <v>1141</v>
       </c>
       <c r="G2" t="n">
-        <v>1438</v>
+        <v>1199</v>
       </c>
       <c r="H2" t="n">
-        <v>1497</v>
+        <v>1202</v>
       </c>
       <c r="I2" t="n">
-        <v>1238</v>
+        <v>1174</v>
       </c>
       <c r="J2" t="n">
-        <v>1428</v>
+        <v>1255</v>
       </c>
       <c r="K2" t="n">
-        <v>1286</v>
+        <v>1023</v>
       </c>
       <c r="L2" t="n">
-        <v>1322.4</v>
+        <v>1175.9</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1237</v>
+        <v>1134</v>
       </c>
       <c r="C3" t="n">
-        <v>1105</v>
+        <v>1068</v>
       </c>
       <c r="D3" t="n">
-        <v>1332</v>
+        <v>1141</v>
       </c>
       <c r="E3" t="n">
-        <v>1291</v>
+        <v>1303</v>
       </c>
       <c r="F3" t="n">
-        <v>1419</v>
+        <v>1060</v>
       </c>
       <c r="G3" t="n">
-        <v>1272</v>
+        <v>1349</v>
       </c>
       <c r="H3" t="n">
-        <v>1399</v>
+        <v>1280</v>
       </c>
       <c r="I3" t="n">
-        <v>1223</v>
+        <v>1115</v>
       </c>
       <c r="J3" t="n">
-        <v>1380</v>
+        <v>1042</v>
       </c>
       <c r="K3" t="n">
-        <v>1149</v>
+        <v>1193</v>
       </c>
       <c r="L3" t="n">
-        <v>1280.7</v>
+        <v>1168.5</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1178</v>
+        <v>1305</v>
       </c>
       <c r="C4" t="n">
-        <v>1164</v>
+        <v>1305</v>
       </c>
       <c r="D4" t="n">
-        <v>1138</v>
+        <v>1117</v>
       </c>
       <c r="E4" t="n">
-        <v>1441</v>
+        <v>1214</v>
       </c>
       <c r="F4" t="n">
-        <v>1559</v>
+        <v>1052</v>
       </c>
       <c r="G4" t="n">
-        <v>1087</v>
+        <v>1329</v>
       </c>
       <c r="H4" t="n">
-        <v>1215</v>
+        <v>1057</v>
       </c>
       <c r="I4" t="n">
-        <v>1237</v>
+        <v>1031</v>
       </c>
       <c r="J4" t="n">
-        <v>1120</v>
+        <v>1213</v>
       </c>
       <c r="K4" t="n">
-        <v>1217</v>
+        <v>1036</v>
       </c>
       <c r="L4" t="n">
-        <v>1235.6</v>
+        <v>1165.9</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1106</v>
+        <v>1002</v>
       </c>
       <c r="C5" t="n">
-        <v>1132</v>
+        <v>1263</v>
       </c>
       <c r="D5" t="n">
-        <v>1057</v>
+        <v>1151</v>
       </c>
       <c r="E5" t="n">
-        <v>1070</v>
+        <v>968</v>
       </c>
       <c r="F5" t="n">
-        <v>941</v>
+        <v>1310</v>
       </c>
       <c r="G5" t="n">
-        <v>1267</v>
+        <v>1035</v>
       </c>
       <c r="H5" t="n">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="I5" t="n">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="J5" t="n">
-        <v>969</v>
+        <v>1130</v>
       </c>
       <c r="K5" t="n">
-        <v>1027</v>
+        <v>1046</v>
       </c>
       <c r="L5" t="n">
-        <v>1067.7</v>
+        <v>1102.7</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1407</v>
+        <v>1185</v>
       </c>
       <c r="C6" t="n">
-        <v>1282</v>
+        <v>1108</v>
       </c>
       <c r="D6" t="n">
-        <v>1338</v>
+        <v>1087</v>
       </c>
       <c r="E6" t="n">
-        <v>1519</v>
+        <v>1075</v>
       </c>
       <c r="F6" t="n">
-        <v>1167</v>
+        <v>1248</v>
       </c>
       <c r="G6" t="n">
+        <v>1085</v>
+      </c>
+      <c r="H6" t="n">
         <v>1118</v>
       </c>
-      <c r="H6" t="n">
-        <v>1336</v>
-      </c>
       <c r="I6" t="n">
-        <v>1215</v>
+        <v>1200</v>
       </c>
       <c r="J6" t="n">
-        <v>1038</v>
+        <v>1176</v>
       </c>
       <c r="K6" t="n">
-        <v>1210</v>
+        <v>1313</v>
       </c>
       <c r="L6" t="n">
-        <v>1263</v>
+        <v>1159.5</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1084</v>
+        <v>1184</v>
       </c>
       <c r="C7" t="n">
-        <v>1331</v>
+        <v>946</v>
       </c>
       <c r="D7" t="n">
+        <v>1156</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1276</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1236</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1009</v>
+      </c>
+      <c r="I7" t="n">
         <v>1256</v>
       </c>
-      <c r="E7" t="n">
-        <v>1053</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1309</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1042</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1293</v>
-      </c>
       <c r="J7" t="n">
-        <v>1056</v>
+        <v>983</v>
       </c>
       <c r="K7" t="n">
-        <v>1233</v>
+        <v>1001</v>
       </c>
       <c r="L7" t="n">
-        <v>1173.7</v>
+        <v>1109.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1179</v>
+        <v>1251</v>
       </c>
       <c r="C8" t="n">
-        <v>1373</v>
+        <v>1094</v>
       </c>
       <c r="D8" t="n">
-        <v>1196</v>
+        <v>1239</v>
       </c>
       <c r="E8" t="n">
-        <v>1125</v>
+        <v>1154</v>
       </c>
       <c r="F8" t="n">
-        <v>1167</v>
+        <v>1023</v>
       </c>
       <c r="G8" t="n">
-        <v>1293</v>
+        <v>1132</v>
       </c>
       <c r="H8" t="n">
-        <v>1489</v>
+        <v>1250</v>
       </c>
       <c r="I8" t="n">
-        <v>1227</v>
+        <v>1082</v>
       </c>
       <c r="J8" t="n">
-        <v>1053</v>
+        <v>1120</v>
       </c>
       <c r="K8" t="n">
-        <v>1453</v>
+        <v>1328</v>
       </c>
       <c r="L8" t="n">
-        <v>1255.5</v>
+        <v>1167.3</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1094</v>
+        <v>1071</v>
       </c>
       <c r="C9" t="n">
-        <v>1126</v>
+        <v>992</v>
       </c>
       <c r="D9" t="n">
-        <v>1052</v>
+        <v>1033</v>
       </c>
       <c r="E9" t="n">
-        <v>1431</v>
+        <v>902</v>
       </c>
       <c r="F9" t="n">
-        <v>1282</v>
+        <v>981</v>
       </c>
       <c r="G9" t="n">
-        <v>1200</v>
+        <v>1287</v>
       </c>
       <c r="H9" t="n">
-        <v>1503</v>
+        <v>1005</v>
       </c>
       <c r="I9" t="n">
-        <v>1169</v>
+        <v>1211</v>
       </c>
       <c r="J9" t="n">
-        <v>1317</v>
+        <v>1213</v>
       </c>
       <c r="K9" t="n">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="L9" t="n">
-        <v>1224</v>
+        <v>1075.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1159</v>
+        <v>1071</v>
       </c>
       <c r="C10" t="n">
-        <v>1113</v>
+        <v>1131</v>
       </c>
       <c r="D10" t="n">
-        <v>1069</v>
+        <v>1204</v>
       </c>
       <c r="E10" t="n">
-        <v>1267</v>
+        <v>1171</v>
       </c>
       <c r="F10" t="n">
-        <v>1134</v>
+        <v>1036</v>
       </c>
       <c r="G10" t="n">
-        <v>1331</v>
+        <v>1194</v>
       </c>
       <c r="H10" t="n">
-        <v>1179</v>
+        <v>1316</v>
       </c>
       <c r="I10" t="n">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="J10" t="n">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="K10" t="n">
-        <v>1117</v>
+        <v>1230</v>
       </c>
       <c r="L10" t="n">
-        <v>1170.2</v>
+        <v>1167.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1368</v>
+        <v>1153</v>
       </c>
       <c r="C11" t="n">
         <v>1204</v>
       </c>
       <c r="D11" t="n">
-        <v>1358</v>
+        <v>1306</v>
       </c>
       <c r="E11" t="n">
-        <v>1371</v>
+        <v>1208</v>
       </c>
       <c r="F11" t="n">
-        <v>1391</v>
+        <v>1151</v>
       </c>
       <c r="G11" t="n">
-        <v>1274</v>
+        <v>1036</v>
       </c>
       <c r="H11" t="n">
-        <v>1249</v>
+        <v>1281</v>
       </c>
       <c r="I11" t="n">
-        <v>1073</v>
+        <v>1091</v>
       </c>
       <c r="J11" t="n">
-        <v>1263</v>
+        <v>1196</v>
       </c>
       <c r="K11" t="n">
-        <v>1062</v>
+        <v>1228</v>
       </c>
       <c r="L11" t="n">
-        <v>1261.3</v>
+        <v>1185.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1313</v>
+        <v>1196</v>
       </c>
       <c r="C12" t="n">
-        <v>1192</v>
+        <v>1206</v>
       </c>
       <c r="D12" t="n">
-        <v>1475</v>
+        <v>1308</v>
       </c>
       <c r="E12" t="n">
-        <v>1208</v>
+        <v>1287</v>
       </c>
       <c r="F12" t="n">
-        <v>1327</v>
+        <v>1360</v>
       </c>
       <c r="G12" t="n">
-        <v>1225</v>
+        <v>1212</v>
       </c>
       <c r="H12" t="n">
-        <v>1380</v>
+        <v>1328</v>
       </c>
       <c r="I12" t="n">
+        <v>1323</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1377</v>
+      </c>
+      <c r="K12" t="n">
         <v>1410</v>
       </c>
-      <c r="J12" t="n">
-        <v>1281</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1286</v>
-      </c>
       <c r="L12" t="n">
-        <v>1309.7</v>
+        <v>1300.7</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C13" t="n">
         <v>1351</v>
       </c>
-      <c r="C13" t="n">
-        <v>1363</v>
-      </c>
       <c r="D13" t="n">
-        <v>1543</v>
+        <v>1294</v>
       </c>
       <c r="E13" t="n">
-        <v>1215</v>
+        <v>1148</v>
       </c>
       <c r="F13" t="n">
-        <v>1497</v>
+        <v>1441</v>
       </c>
       <c r="G13" t="n">
-        <v>1152</v>
+        <v>1238</v>
       </c>
       <c r="H13" t="n">
-        <v>1043</v>
+        <v>1163</v>
       </c>
       <c r="I13" t="n">
-        <v>1202</v>
+        <v>1244</v>
       </c>
       <c r="J13" t="n">
-        <v>1088</v>
+        <v>1165</v>
       </c>
       <c r="K13" t="n">
-        <v>1172</v>
+        <v>1121</v>
       </c>
       <c r="L13" t="n">
-        <v>1262.6</v>
+        <v>1245.9</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1295</v>
+        <v>1076</v>
       </c>
       <c r="C14" t="n">
-        <v>1203</v>
+        <v>1014</v>
       </c>
       <c r="D14" t="n">
-        <v>1299</v>
+        <v>968</v>
       </c>
       <c r="E14" t="n">
-        <v>1034</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="n">
-        <v>1250</v>
+        <v>1193</v>
       </c>
       <c r="G14" t="n">
-        <v>1031</v>
+        <v>1185</v>
       </c>
       <c r="H14" t="n">
-        <v>1108</v>
+        <v>1277</v>
       </c>
       <c r="I14" t="n">
-        <v>1367</v>
+        <v>1331</v>
       </c>
       <c r="J14" t="n">
-        <v>1113</v>
+        <v>1352</v>
       </c>
       <c r="K14" t="n">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="L14" t="n">
-        <v>1174.3</v>
+        <v>1148.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1391</v>
+        <v>1136</v>
       </c>
       <c r="C15" t="n">
-        <v>1382</v>
+        <v>1339</v>
       </c>
       <c r="D15" t="n">
-        <v>1278</v>
+        <v>1036</v>
       </c>
       <c r="E15" t="n">
-        <v>1171</v>
+        <v>1056</v>
       </c>
       <c r="F15" t="n">
-        <v>1195</v>
+        <v>1301</v>
       </c>
       <c r="G15" t="n">
-        <v>1228</v>
+        <v>1247</v>
       </c>
       <c r="H15" t="n">
-        <v>1425</v>
+        <v>1235</v>
       </c>
       <c r="I15" t="n">
-        <v>1138</v>
+        <v>1368</v>
       </c>
       <c r="J15" t="n">
-        <v>1162</v>
+        <v>1249</v>
       </c>
       <c r="K15" t="n">
-        <v>1250</v>
+        <v>1213</v>
       </c>
       <c r="L15" t="n">
-        <v>1262</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1580</v>
+        <v>960</v>
       </c>
       <c r="C16" t="n">
-        <v>1299</v>
+        <v>1217</v>
       </c>
       <c r="D16" t="n">
-        <v>1292</v>
+        <v>1031</v>
       </c>
       <c r="E16" t="n">
-        <v>1353</v>
+        <v>1200</v>
       </c>
       <c r="F16" t="n">
-        <v>1313</v>
+        <v>1119</v>
       </c>
       <c r="G16" t="n">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="H16" t="n">
-        <v>1265</v>
+        <v>1119</v>
       </c>
       <c r="I16" t="n">
-        <v>1089</v>
+        <v>1116</v>
       </c>
       <c r="J16" t="n">
-        <v>1257</v>
+        <v>1082</v>
       </c>
       <c r="K16" t="n">
-        <v>1379</v>
+        <v>1210</v>
       </c>
       <c r="L16" t="n">
-        <v>1316.4</v>
+        <v>1139.5</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1256</v>
+        <v>1154</v>
       </c>
       <c r="C17" t="n">
-        <v>1290</v>
+        <v>1109</v>
       </c>
       <c r="D17" t="n">
-        <v>1241</v>
+        <v>1164</v>
       </c>
       <c r="E17" t="n">
-        <v>1412</v>
+        <v>1247</v>
       </c>
       <c r="F17" t="n">
-        <v>1429</v>
+        <v>1128</v>
       </c>
       <c r="G17" t="n">
-        <v>1590</v>
+        <v>1263</v>
       </c>
       <c r="H17" t="n">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="I17" t="n">
-        <v>1488</v>
+        <v>1139</v>
       </c>
       <c r="J17" t="n">
-        <v>1235</v>
+        <v>1003</v>
       </c>
       <c r="K17" t="n">
-        <v>1432</v>
+        <v>1274</v>
       </c>
       <c r="L17" t="n">
-        <v>1352.6</v>
+        <v>1164.7</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1139</v>
+        <v>1213</v>
       </c>
       <c r="C18" t="n">
-        <v>1012</v>
+        <v>1251</v>
       </c>
       <c r="D18" t="n">
-        <v>1311</v>
+        <v>1155</v>
       </c>
       <c r="E18" t="n">
-        <v>1096</v>
+        <v>1316</v>
       </c>
       <c r="F18" t="n">
-        <v>1105</v>
+        <v>1145</v>
       </c>
       <c r="G18" t="n">
-        <v>1104</v>
+        <v>1324</v>
       </c>
       <c r="H18" t="n">
-        <v>1084</v>
+        <v>1058</v>
       </c>
       <c r="I18" t="n">
-        <v>1108</v>
+        <v>1237</v>
       </c>
       <c r="J18" t="n">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="K18" t="n">
-        <v>1218</v>
+        <v>1070</v>
       </c>
       <c r="L18" t="n">
-        <v>1127.8</v>
+        <v>1186.9</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1100</v>
+        <v>1354</v>
       </c>
       <c r="C19" t="n">
-        <v>1341</v>
+        <v>1408</v>
       </c>
       <c r="D19" t="n">
-        <v>1179</v>
+        <v>1125</v>
       </c>
       <c r="E19" t="n">
-        <v>1403</v>
+        <v>1307</v>
       </c>
       <c r="F19" t="n">
-        <v>1268</v>
+        <v>1229</v>
       </c>
       <c r="G19" t="n">
-        <v>1210</v>
+        <v>1360</v>
       </c>
       <c r="H19" t="n">
-        <v>1394</v>
+        <v>1301</v>
       </c>
       <c r="I19" t="n">
-        <v>1235</v>
+        <v>1127</v>
       </c>
       <c r="J19" t="n">
-        <v>1212</v>
+        <v>1441</v>
       </c>
       <c r="K19" t="n">
-        <v>1032</v>
+        <v>1326</v>
       </c>
       <c r="L19" t="n">
-        <v>1237.4</v>
+        <v>1297.8</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1321</v>
+        <v>1183</v>
       </c>
       <c r="C20" t="n">
-        <v>1261</v>
+        <v>1248</v>
       </c>
       <c r="D20" t="n">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="E20" t="n">
-        <v>1203</v>
+        <v>1297</v>
       </c>
       <c r="F20" t="n">
-        <v>1584</v>
+        <v>1290</v>
       </c>
       <c r="G20" t="n">
-        <v>1318</v>
+        <v>1271</v>
       </c>
       <c r="H20" t="n">
-        <v>1398</v>
+        <v>1301</v>
       </c>
       <c r="I20" t="n">
-        <v>1202</v>
+        <v>1276</v>
       </c>
       <c r="J20" t="n">
-        <v>1260</v>
+        <v>1247</v>
       </c>
       <c r="K20" t="n">
-        <v>1307</v>
+        <v>1221</v>
       </c>
       <c r="L20" t="n">
-        <v>1317.8</v>
+        <v>1265.2</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1177</v>
+        <v>1094</v>
       </c>
       <c r="C21" t="n">
-        <v>1190</v>
+        <v>1162</v>
       </c>
       <c r="D21" t="n">
-        <v>1433</v>
+        <v>1173</v>
       </c>
       <c r="E21" t="n">
-        <v>1283</v>
+        <v>1069</v>
       </c>
       <c r="F21" t="n">
-        <v>1614</v>
+        <v>1168</v>
       </c>
       <c r="G21" t="n">
-        <v>1227</v>
+        <v>1284</v>
       </c>
       <c r="H21" t="n">
-        <v>1285</v>
+        <v>1058</v>
       </c>
       <c r="I21" t="n">
-        <v>1425</v>
+        <v>1200</v>
       </c>
       <c r="J21" t="n">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="K21" t="n">
-        <v>1223</v>
+        <v>1259</v>
       </c>
       <c r="L21" t="n">
-        <v>1308</v>
+        <v>1168.5</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1252</v>
+        <v>1462</v>
       </c>
       <c r="C22" t="n">
-        <v>1194</v>
+        <v>1150</v>
       </c>
       <c r="D22" t="n">
-        <v>1334</v>
+        <v>1203</v>
       </c>
       <c r="E22" t="n">
-        <v>1217</v>
+        <v>1089</v>
       </c>
       <c r="F22" t="n">
-        <v>1183</v>
+        <v>1259</v>
       </c>
       <c r="G22" t="n">
-        <v>1263</v>
+        <v>1369</v>
       </c>
       <c r="H22" t="n">
-        <v>1413</v>
+        <v>1321</v>
       </c>
       <c r="I22" t="n">
-        <v>1223</v>
+        <v>1255</v>
       </c>
       <c r="J22" t="n">
-        <v>1238</v>
+        <v>1366</v>
       </c>
       <c r="K22" t="n">
-        <v>1311</v>
+        <v>1268</v>
       </c>
       <c r="L22" t="n">
-        <v>1262.8</v>
+        <v>1274.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1119</v>
+        <v>1259</v>
       </c>
       <c r="C23" t="n">
-        <v>1067</v>
+        <v>1261</v>
       </c>
       <c r="D23" t="n">
-        <v>1077</v>
+        <v>1089</v>
       </c>
       <c r="E23" t="n">
-        <v>1311</v>
+        <v>1094</v>
       </c>
       <c r="F23" t="n">
-        <v>1160</v>
+        <v>1046</v>
       </c>
       <c r="G23" t="n">
-        <v>1113</v>
+        <v>1215</v>
       </c>
       <c r="H23" t="n">
-        <v>1219</v>
+        <v>1301</v>
       </c>
       <c r="I23" t="n">
-        <v>1259</v>
+        <v>1065</v>
       </c>
       <c r="J23" t="n">
-        <v>1041</v>
+        <v>1079</v>
       </c>
       <c r="K23" t="n">
-        <v>1285</v>
+        <v>1001</v>
       </c>
       <c r="L23" t="n">
-        <v>1165.1</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1158</v>
+        <v>1304</v>
       </c>
       <c r="C24" t="n">
-        <v>1250</v>
+        <v>1027</v>
       </c>
       <c r="D24" t="n">
-        <v>1381</v>
+        <v>1075</v>
       </c>
       <c r="E24" t="n">
-        <v>1274</v>
+        <v>1221</v>
       </c>
       <c r="F24" t="n">
-        <v>1284</v>
+        <v>1228</v>
       </c>
       <c r="G24" t="n">
-        <v>1174</v>
+        <v>1224</v>
       </c>
       <c r="H24" t="n">
-        <v>1352</v>
+        <v>1268</v>
       </c>
       <c r="I24" t="n">
-        <v>1432</v>
+        <v>1001</v>
       </c>
       <c r="J24" t="n">
-        <v>1136</v>
+        <v>1167</v>
       </c>
       <c r="K24" t="n">
-        <v>1427</v>
+        <v>1236</v>
       </c>
       <c r="L24" t="n">
-        <v>1286.8</v>
+        <v>1175.1</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1468</v>
+        <v>1208</v>
       </c>
       <c r="C25" t="n">
-        <v>1183</v>
+        <v>1074</v>
       </c>
       <c r="D25" t="n">
-        <v>1178</v>
+        <v>1329</v>
       </c>
       <c r="E25" t="n">
-        <v>1188</v>
+        <v>1328</v>
       </c>
       <c r="F25" t="n">
-        <v>1360</v>
+        <v>1334</v>
       </c>
       <c r="G25" t="n">
-        <v>1223</v>
+        <v>1314</v>
       </c>
       <c r="H25" t="n">
-        <v>1053</v>
+        <v>1349</v>
       </c>
       <c r="I25" t="n">
-        <v>1526</v>
+        <v>1160</v>
       </c>
       <c r="J25" t="n">
-        <v>1307</v>
+        <v>1396</v>
       </c>
       <c r="K25" t="n">
-        <v>1258</v>
+        <v>1442</v>
       </c>
       <c r="L25" t="n">
-        <v>1274.4</v>
+        <v>1293.4</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1168</v>
+        <v>1090</v>
       </c>
       <c r="C26" t="n">
-        <v>1335</v>
+        <v>1055</v>
       </c>
       <c r="D26" t="n">
-        <v>1275</v>
+        <v>1059</v>
       </c>
       <c r="E26" t="n">
-        <v>1184</v>
+        <v>1058</v>
       </c>
       <c r="F26" t="n">
-        <v>1212</v>
+        <v>1035</v>
       </c>
       <c r="G26" t="n">
-        <v>1142</v>
+        <v>985</v>
       </c>
       <c r="H26" t="n">
-        <v>1080</v>
+        <v>1133</v>
       </c>
       <c r="I26" t="n">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="J26" t="n">
-        <v>1157</v>
+        <v>1082</v>
       </c>
       <c r="K26" t="n">
-        <v>1067</v>
+        <v>1230</v>
       </c>
       <c r="L26" t="n">
-        <v>1180.5</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1321</v>
+        <v>1234</v>
       </c>
       <c r="C27" t="n">
-        <v>1256</v>
+        <v>1170</v>
       </c>
       <c r="D27" t="n">
-        <v>1476</v>
+        <v>1280</v>
       </c>
       <c r="E27" t="n">
-        <v>1294</v>
+        <v>1170</v>
       </c>
       <c r="F27" t="n">
-        <v>1109</v>
+        <v>1187</v>
       </c>
       <c r="G27" t="n">
-        <v>1118</v>
+        <v>1132</v>
       </c>
       <c r="H27" t="n">
-        <v>1494</v>
+        <v>1395</v>
       </c>
       <c r="I27" t="n">
-        <v>1317</v>
+        <v>1188</v>
       </c>
       <c r="J27" t="n">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="K27" t="n">
-        <v>1520</v>
+        <v>1169</v>
       </c>
       <c r="L27" t="n">
-        <v>1309.7</v>
+        <v>1211.9</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1257</v>
+        <v>1451</v>
       </c>
       <c r="C28" t="n">
+        <v>1212</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1102</v>
+      </c>
+      <c r="E28" t="n">
         <v>1063</v>
       </c>
-      <c r="D28" t="n">
-        <v>1072</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1251</v>
-      </c>
       <c r="F28" t="n">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="G28" t="n">
-        <v>1337</v>
+        <v>1116</v>
       </c>
       <c r="H28" t="n">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="I28" t="n">
-        <v>1218</v>
+        <v>1168</v>
       </c>
       <c r="J28" t="n">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="K28" t="n">
-        <v>1062</v>
+        <v>1229</v>
       </c>
       <c r="L28" t="n">
-        <v>1167.2</v>
+        <v>1176.8</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="C29" t="n">
-        <v>1359</v>
+        <v>980</v>
       </c>
       <c r="D29" t="n">
-        <v>1370</v>
+        <v>1129</v>
       </c>
       <c r="E29" t="n">
-        <v>1356</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="n">
-        <v>1534</v>
+        <v>988</v>
       </c>
       <c r="G29" t="n">
-        <v>1128</v>
+        <v>1054</v>
       </c>
       <c r="H29" t="n">
-        <v>1384</v>
+        <v>1202</v>
       </c>
       <c r="I29" t="n">
-        <v>1212</v>
+        <v>1092</v>
       </c>
       <c r="J29" t="n">
-        <v>1527</v>
+        <v>1093</v>
       </c>
       <c r="K29" t="n">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="L29" t="n">
-        <v>1318.4</v>
+        <v>1073.3</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1342</v>
+        <v>1282</v>
       </c>
       <c r="C30" t="n">
-        <v>1142</v>
+        <v>994</v>
       </c>
       <c r="D30" t="n">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="E30" t="n">
-        <v>1193</v>
+        <v>957</v>
       </c>
       <c r="F30" t="n">
-        <v>1357</v>
+        <v>1160</v>
       </c>
       <c r="G30" t="n">
-        <v>1121</v>
+        <v>1211</v>
       </c>
       <c r="H30" t="n">
-        <v>1081</v>
+        <v>1320</v>
       </c>
       <c r="I30" t="n">
-        <v>1071</v>
+        <v>1058</v>
       </c>
       <c r="J30" t="n">
-        <v>1059</v>
+        <v>1040</v>
       </c>
       <c r="K30" t="n">
-        <v>1064</v>
+        <v>1230</v>
       </c>
       <c r="L30" t="n">
-        <v>1160</v>
+        <v>1144.9</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1237</v>
+        <v>1314</v>
       </c>
       <c r="C31" t="n">
-        <v>1337</v>
+        <v>1205</v>
       </c>
       <c r="D31" t="n">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="E31" t="n">
-        <v>1323</v>
+        <v>1113</v>
       </c>
       <c r="F31" t="n">
-        <v>1305</v>
+        <v>1221</v>
       </c>
       <c r="G31" t="n">
-        <v>1137</v>
+        <v>1267</v>
       </c>
       <c r="H31" t="n">
-        <v>1245</v>
+        <v>1023</v>
       </c>
       <c r="I31" t="n">
-        <v>1049</v>
+        <v>1264</v>
       </c>
       <c r="J31" t="n">
-        <v>1404</v>
+        <v>1186</v>
       </c>
       <c r="K31" t="n">
-        <v>1314</v>
+        <v>1144</v>
       </c>
       <c r="L31" t="n">
-        <v>1262.8</v>
+        <v>1200.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1319</v>
+        <v>976</v>
       </c>
       <c r="C32" t="n">
-        <v>1028</v>
+        <v>1135</v>
       </c>
       <c r="D32" t="n">
-        <v>1100</v>
+        <v>1065</v>
       </c>
       <c r="E32" t="n">
-        <v>1336</v>
+        <v>1047</v>
       </c>
       <c r="F32" t="n">
-        <v>1024</v>
+        <v>962</v>
       </c>
       <c r="G32" t="n">
-        <v>1108</v>
+        <v>1038</v>
       </c>
       <c r="H32" t="n">
-        <v>1237</v>
+        <v>1035</v>
       </c>
       <c r="I32" t="n">
-        <v>1128</v>
+        <v>1003</v>
       </c>
       <c r="J32" t="n">
-        <v>1220</v>
+        <v>960</v>
       </c>
       <c r="K32" t="n">
-        <v>1175</v>
+        <v>1109</v>
       </c>
       <c r="L32" t="n">
-        <v>1167.5</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1458</v>
+        <v>1121</v>
       </c>
       <c r="C33" t="n">
-        <v>1275</v>
+        <v>1077</v>
       </c>
       <c r="D33" t="n">
-        <v>1220</v>
+        <v>1240</v>
       </c>
       <c r="E33" t="n">
-        <v>1392</v>
+        <v>1182</v>
       </c>
       <c r="F33" t="n">
-        <v>1195</v>
+        <v>1052</v>
       </c>
       <c r="G33" t="n">
-        <v>1234</v>
+        <v>1018</v>
       </c>
       <c r="H33" t="n">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="I33" t="n">
-        <v>1232</v>
+        <v>1254</v>
       </c>
       <c r="J33" t="n">
-        <v>1100</v>
+        <v>1180</v>
       </c>
       <c r="K33" t="n">
-        <v>1276</v>
+        <v>1155</v>
       </c>
       <c r="L33" t="n">
-        <v>1249.4</v>
+        <v>1137.5</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1276</v>
+        <v>1047</v>
       </c>
       <c r="C34" t="n">
-        <v>1117</v>
+        <v>1008</v>
       </c>
       <c r="D34" t="n">
-        <v>1296</v>
+        <v>1155</v>
       </c>
       <c r="E34" t="n">
-        <v>1081</v>
+        <v>1139</v>
       </c>
       <c r="F34" t="n">
-        <v>1285</v>
+        <v>1134</v>
       </c>
       <c r="G34" t="n">
-        <v>1145</v>
+        <v>1191</v>
       </c>
       <c r="H34" t="n">
-        <v>1311</v>
+        <v>1068</v>
       </c>
       <c r="I34" t="n">
-        <v>1137</v>
+        <v>1174</v>
       </c>
       <c r="J34" t="n">
-        <v>1093</v>
+        <v>1063</v>
       </c>
       <c r="K34" t="n">
-        <v>1173</v>
+        <v>1055</v>
       </c>
       <c r="L34" t="n">
-        <v>1191.4</v>
+        <v>1103.4</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1156</v>
+        <v>1294</v>
       </c>
       <c r="C35" t="n">
-        <v>1258</v>
+        <v>1313</v>
       </c>
       <c r="D35" t="n">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="E35" t="n">
-        <v>1166</v>
+        <v>1348</v>
       </c>
       <c r="F35" t="n">
-        <v>1421</v>
+        <v>1306</v>
       </c>
       <c r="G35" t="n">
-        <v>1280</v>
+        <v>1129</v>
       </c>
       <c r="H35" t="n">
-        <v>1202</v>
+        <v>1046</v>
       </c>
       <c r="I35" t="n">
-        <v>1312</v>
+        <v>1076</v>
       </c>
       <c r="J35" t="n">
-        <v>1383</v>
+        <v>1032</v>
       </c>
       <c r="K35" t="n">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="L35" t="n">
-        <v>1249.1</v>
+        <v>1186.3</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1255</v>
+        <v>1186</v>
       </c>
       <c r="C36" t="n">
-        <v>1264</v>
+        <v>935</v>
       </c>
       <c r="D36" t="n">
-        <v>1091</v>
+        <v>1258</v>
       </c>
       <c r="E36" t="n">
-        <v>1184</v>
+        <v>947</v>
       </c>
       <c r="F36" t="n">
-        <v>1207</v>
+        <v>1117</v>
       </c>
       <c r="G36" t="n">
-        <v>1162</v>
+        <v>1034</v>
       </c>
       <c r="H36" t="n">
+        <v>1119</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1009</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1131</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1114</v>
+      </c>
+      <c r="L36" t="n">
         <v>1085</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1414</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1215</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1049</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1192.6</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1307</v>
+        <v>1078</v>
       </c>
       <c r="C37" t="n">
-        <v>1418</v>
+        <v>1221</v>
       </c>
       <c r="D37" t="n">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="E37" t="n">
-        <v>1144</v>
+        <v>1305</v>
       </c>
       <c r="F37" t="n">
-        <v>1139</v>
+        <v>1256</v>
       </c>
       <c r="G37" t="n">
-        <v>1188</v>
+        <v>1061</v>
       </c>
       <c r="H37" t="n">
-        <v>1384</v>
+        <v>1125</v>
       </c>
       <c r="I37" t="n">
-        <v>1113</v>
+        <v>1133</v>
       </c>
       <c r="J37" t="n">
-        <v>1139</v>
+        <v>1049</v>
       </c>
       <c r="K37" t="n">
-        <v>1406</v>
+        <v>1391</v>
       </c>
       <c r="L37" t="n">
-        <v>1249.3</v>
+        <v>1186.9</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1129</v>
+        <v>1272</v>
       </c>
       <c r="C38" t="n">
-        <v>1225</v>
+        <v>1272</v>
       </c>
       <c r="D38" t="n">
-        <v>1385</v>
+        <v>1230</v>
       </c>
       <c r="E38" t="n">
-        <v>1244</v>
+        <v>1126</v>
       </c>
       <c r="F38" t="n">
-        <v>1101</v>
+        <v>962</v>
       </c>
       <c r="G38" t="n">
-        <v>1103</v>
+        <v>1059</v>
       </c>
       <c r="H38" t="n">
-        <v>1451</v>
+        <v>1317</v>
       </c>
       <c r="I38" t="n">
-        <v>1447</v>
+        <v>1159</v>
       </c>
       <c r="J38" t="n">
-        <v>1128</v>
+        <v>1078</v>
       </c>
       <c r="K38" t="n">
-        <v>1157</v>
+        <v>1086</v>
       </c>
       <c r="L38" t="n">
-        <v>1237</v>
+        <v>1156.1</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1023</v>
+        <v>1120</v>
       </c>
       <c r="C39" t="n">
-        <v>1153</v>
+        <v>1188</v>
       </c>
       <c r="D39" t="n">
-        <v>1137</v>
+        <v>1169</v>
       </c>
       <c r="E39" t="n">
-        <v>1247</v>
+        <v>1105</v>
       </c>
       <c r="F39" t="n">
-        <v>1317</v>
+        <v>1053</v>
       </c>
       <c r="G39" t="n">
-        <v>1024</v>
+        <v>1091</v>
       </c>
       <c r="H39" t="n">
-        <v>1227</v>
+        <v>1390</v>
       </c>
       <c r="I39" t="n">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="J39" t="n">
-        <v>1104</v>
+        <v>1184</v>
       </c>
       <c r="K39" t="n">
-        <v>1528</v>
+        <v>989</v>
       </c>
       <c r="L39" t="n">
-        <v>1184.2</v>
+        <v>1138.2</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1004</v>
+        <v>1158</v>
       </c>
       <c r="C40" t="n">
-        <v>1122</v>
+        <v>1180</v>
       </c>
       <c r="D40" t="n">
-        <v>1334</v>
+        <v>1184</v>
       </c>
       <c r="E40" t="n">
-        <v>1029</v>
+        <v>1129</v>
       </c>
       <c r="F40" t="n">
-        <v>1154</v>
+        <v>1249</v>
       </c>
       <c r="G40" t="n">
-        <v>1227</v>
+        <v>1187</v>
       </c>
       <c r="H40" t="n">
-        <v>1313</v>
+        <v>1180</v>
       </c>
       <c r="I40" t="n">
-        <v>1078</v>
+        <v>1259</v>
       </c>
       <c r="J40" t="n">
-        <v>1384</v>
+        <v>1117</v>
       </c>
       <c r="K40" t="n">
-        <v>1365</v>
+        <v>1113</v>
       </c>
       <c r="L40" t="n">
-        <v>1201</v>
+        <v>1175.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1463</v>
+        <v>1160</v>
       </c>
       <c r="C41" t="n">
-        <v>1320</v>
+        <v>885</v>
       </c>
       <c r="D41" t="n">
-        <v>1173</v>
+        <v>1072</v>
       </c>
       <c r="E41" t="n">
-        <v>1411</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="n">
-        <v>1194</v>
+        <v>1176</v>
       </c>
       <c r="G41" t="n">
-        <v>1123</v>
+        <v>1153</v>
       </c>
       <c r="H41" t="n">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="I41" t="n">
-        <v>1376</v>
+        <v>1206</v>
       </c>
       <c r="J41" t="n">
-        <v>1186</v>
+        <v>1201</v>
       </c>
       <c r="K41" t="n">
-        <v>1101</v>
+        <v>1132</v>
       </c>
       <c r="L41" t="n">
-        <v>1239.2</v>
+        <v>1123.5</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>999</v>
+        <v>1265</v>
       </c>
       <c r="C42" t="n">
-        <v>1288</v>
+        <v>1180</v>
       </c>
       <c r="D42" t="n">
-        <v>1136</v>
+        <v>1155</v>
       </c>
       <c r="E42" t="n">
-        <v>1277</v>
+        <v>1284</v>
       </c>
       <c r="F42" t="n">
-        <v>1293</v>
+        <v>1117</v>
       </c>
       <c r="G42" t="n">
-        <v>1171</v>
+        <v>1030</v>
       </c>
       <c r="H42" t="n">
-        <v>1255</v>
+        <v>1036</v>
       </c>
       <c r="I42" t="n">
-        <v>1311</v>
+        <v>1054</v>
       </c>
       <c r="J42" t="n">
-        <v>1180</v>
+        <v>1119</v>
       </c>
       <c r="K42" t="n">
-        <v>1092</v>
+        <v>1155</v>
       </c>
       <c r="L42" t="n">
-        <v>1200.2</v>
+        <v>1139.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1048</v>
+        <v>1091</v>
       </c>
       <c r="C43" t="n">
-        <v>1192</v>
+        <v>1271</v>
       </c>
       <c r="D43" t="n">
-        <v>1148</v>
+        <v>1086</v>
       </c>
       <c r="E43" t="n">
-        <v>1078</v>
+        <v>1087</v>
       </c>
       <c r="F43" t="n">
-        <v>1293</v>
+        <v>1216</v>
       </c>
       <c r="G43" t="n">
-        <v>1102</v>
+        <v>1423</v>
       </c>
       <c r="H43" t="n">
-        <v>1425</v>
+        <v>1203</v>
       </c>
       <c r="I43" t="n">
-        <v>1281</v>
+        <v>1220</v>
       </c>
       <c r="J43" t="n">
-        <v>1489</v>
+        <v>1173</v>
       </c>
       <c r="K43" t="n">
-        <v>1348</v>
+        <v>1216</v>
       </c>
       <c r="L43" t="n">
-        <v>1240.4</v>
+        <v>1198.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1448</v>
+        <v>1417</v>
       </c>
       <c r="C44" t="n">
-        <v>1467</v>
+        <v>1302</v>
       </c>
       <c r="D44" t="n">
-        <v>1301</v>
+        <v>1377</v>
       </c>
       <c r="E44" t="n">
-        <v>1277</v>
+        <v>1261</v>
       </c>
       <c r="F44" t="n">
-        <v>1190</v>
+        <v>1297</v>
       </c>
       <c r="G44" t="n">
-        <v>1073</v>
+        <v>1157</v>
       </c>
       <c r="H44" t="n">
-        <v>1172</v>
+        <v>1235</v>
       </c>
       <c r="I44" t="n">
-        <v>1108</v>
+        <v>1291</v>
       </c>
       <c r="J44" t="n">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="K44" t="n">
-        <v>1392</v>
+        <v>1293</v>
       </c>
       <c r="L44" t="n">
-        <v>1272.5</v>
+        <v>1293.3</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
+        <v>1264</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1071</v>
+      </c>
+      <c r="D45" t="n">
+        <v>991</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1261</v>
+      </c>
+      <c r="F45" t="n">
+        <v>999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1104</v>
+      </c>
+      <c r="H45" t="n">
         <v>1210</v>
       </c>
-      <c r="C45" t="n">
-        <v>1223</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1123</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1245</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1168</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1315</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1069</v>
-      </c>
       <c r="I45" t="n">
-        <v>1179</v>
+        <v>1340</v>
       </c>
       <c r="J45" t="n">
-        <v>1178</v>
+        <v>1093</v>
       </c>
       <c r="K45" t="n">
-        <v>1121</v>
+        <v>1247</v>
       </c>
       <c r="L45" t="n">
-        <v>1183.1</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1517</v>
+        <v>1218</v>
       </c>
       <c r="C46" t="n">
-        <v>1468</v>
+        <v>1342</v>
       </c>
       <c r="D46" t="n">
-        <v>1434</v>
+        <v>1189</v>
       </c>
       <c r="E46" t="n">
-        <v>1390</v>
+        <v>1181</v>
       </c>
       <c r="F46" t="n">
-        <v>1243</v>
+        <v>1423</v>
       </c>
       <c r="G46" t="n">
-        <v>1313</v>
+        <v>1401</v>
       </c>
       <c r="H46" t="n">
-        <v>1443</v>
+        <v>1254</v>
       </c>
       <c r="I46" t="n">
-        <v>1367</v>
+        <v>1234</v>
       </c>
       <c r="J46" t="n">
-        <v>1169</v>
+        <v>1269</v>
       </c>
       <c r="K46" t="n">
-        <v>1492</v>
+        <v>1275</v>
       </c>
       <c r="L46" t="n">
-        <v>1383.6</v>
+        <v>1278.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1228</v>
+        <v>1379</v>
       </c>
       <c r="C47" t="n">
-        <v>1151</v>
+        <v>1218</v>
       </c>
       <c r="D47" t="n">
-        <v>1275</v>
+        <v>1380</v>
       </c>
       <c r="E47" t="n">
-        <v>1329</v>
+        <v>1293</v>
       </c>
       <c r="F47" t="n">
-        <v>1231</v>
+        <v>1345</v>
       </c>
       <c r="G47" t="n">
-        <v>1294</v>
+        <v>1116</v>
       </c>
       <c r="H47" t="n">
-        <v>1287</v>
+        <v>1355</v>
       </c>
       <c r="I47" t="n">
-        <v>1493</v>
+        <v>1070</v>
       </c>
       <c r="J47" t="n">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="K47" t="n">
-        <v>1220</v>
+        <v>1374</v>
       </c>
       <c r="L47" t="n">
-        <v>1280.3</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1269</v>
+        <v>1160</v>
       </c>
       <c r="C48" t="n">
-        <v>1496</v>
+        <v>1445</v>
       </c>
       <c r="D48" t="n">
-        <v>1250</v>
+        <v>1054</v>
       </c>
       <c r="E48" t="n">
-        <v>1515</v>
+        <v>1150</v>
       </c>
       <c r="F48" t="n">
-        <v>1513</v>
+        <v>1101</v>
       </c>
       <c r="G48" t="n">
-        <v>1395</v>
+        <v>1305</v>
       </c>
       <c r="H48" t="n">
-        <v>1419</v>
+        <v>1034</v>
       </c>
       <c r="I48" t="n">
-        <v>1159</v>
+        <v>1247</v>
       </c>
       <c r="J48" t="n">
-        <v>1298</v>
+        <v>1276</v>
       </c>
       <c r="K48" t="n">
-        <v>1433</v>
+        <v>1156</v>
       </c>
       <c r="L48" t="n">
-        <v>1374.7</v>
+        <v>1192.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1207</v>
+        <v>1044</v>
       </c>
       <c r="C49" t="n">
-        <v>1209</v>
+        <v>1113</v>
       </c>
       <c r="D49" t="n">
-        <v>1467</v>
+        <v>1264</v>
       </c>
       <c r="E49" t="n">
-        <v>1129</v>
+        <v>1321</v>
       </c>
       <c r="F49" t="n">
-        <v>1348</v>
+        <v>1222</v>
       </c>
       <c r="G49" t="n">
-        <v>1421</v>
+        <v>1338</v>
       </c>
       <c r="H49" t="n">
+        <v>1125</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1307</v>
+      </c>
+      <c r="J49" t="n">
         <v>1190</v>
       </c>
-      <c r="I49" t="n">
-        <v>1138</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1267</v>
-      </c>
       <c r="K49" t="n">
-        <v>1114</v>
+        <v>1237</v>
       </c>
       <c r="L49" t="n">
-        <v>1249</v>
+        <v>1216.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1163</v>
+        <v>1008</v>
       </c>
       <c r="C50" t="n">
-        <v>1172</v>
+        <v>1201</v>
       </c>
       <c r="D50" t="n">
-        <v>1144</v>
+        <v>1023</v>
       </c>
       <c r="E50" t="n">
-        <v>1075</v>
+        <v>924</v>
       </c>
       <c r="F50" t="n">
-        <v>1246</v>
+        <v>1069</v>
       </c>
       <c r="G50" t="n">
-        <v>1041</v>
+        <v>1029</v>
       </c>
       <c r="H50" t="n">
-        <v>981</v>
+        <v>1189</v>
       </c>
       <c r="I50" t="n">
-        <v>1176</v>
+        <v>1159</v>
       </c>
       <c r="J50" t="n">
-        <v>1063</v>
+        <v>1145</v>
       </c>
       <c r="K50" t="n">
-        <v>1205</v>
+        <v>1020</v>
       </c>
       <c r="L50" t="n">
-        <v>1126.6</v>
+        <v>1076.7</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1155</v>
+        <v>1051</v>
       </c>
       <c r="C51" t="n">
-        <v>973</v>
+        <v>1163</v>
       </c>
       <c r="D51" t="n">
-        <v>1131</v>
+        <v>1197</v>
       </c>
       <c r="E51" t="n">
-        <v>1121</v>
+        <v>1185</v>
       </c>
       <c r="F51" t="n">
-        <v>1054</v>
+        <v>1088</v>
       </c>
       <c r="G51" t="n">
-        <v>1132</v>
+        <v>1007</v>
       </c>
       <c r="H51" t="n">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="I51" t="n">
+        <v>1053</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1030</v>
+      </c>
+      <c r="K51" t="n">
         <v>1083</v>
       </c>
-      <c r="J51" t="n">
-        <v>1156</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1328</v>
-      </c>
       <c r="L51" t="n">
-        <v>1126.1</v>
+        <v>1099.8</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1244.86</v>
+        <v>1186.18</v>
       </c>
       <c r="C52" t="n">
-        <v>1233.42</v>
+        <v>1164.64</v>
       </c>
       <c r="D52" t="n">
-        <v>1251.78</v>
+        <v>1167.36</v>
       </c>
       <c r="E52" t="n">
-        <v>1252.46</v>
+        <v>1160.92</v>
       </c>
       <c r="F52" t="n">
-        <v>1264.54</v>
+        <v>1162.56</v>
       </c>
       <c r="G52" t="n">
-        <v>1207.02</v>
+        <v>1187.3</v>
       </c>
       <c r="H52" t="n">
-        <v>1255.36</v>
+        <v>1185.62</v>
       </c>
       <c r="I52" t="n">
-        <v>1234.2</v>
+        <v>1170.96</v>
       </c>
       <c r="J52" t="n">
-        <v>1204.48</v>
+        <v>1166.54</v>
       </c>
       <c r="K52" t="n">
-        <v>1233.4</v>
+        <v>1179.32</v>
       </c>
       <c r="L52" t="n">
-        <v>1238.152</v>
+        <v>1173.14</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>15.56511688232422</v>
+        <v>15.86604499816895</v>
       </c>
       <c r="C2" t="n">
-        <v>12.88366198539734</v>
+        <v>13.42802691459656</v>
       </c>
       <c r="D2" t="n">
-        <v>14.91742444038391</v>
+        <v>14.86571073532104</v>
       </c>
       <c r="E2" t="n">
-        <v>16.24740314483643</v>
+        <v>14.89741206169128</v>
       </c>
       <c r="F2" t="n">
-        <v>11.9428985118866</v>
+        <v>13.04026174545288</v>
       </c>
       <c r="G2" t="n">
-        <v>16.51822376251221</v>
+        <v>15.70903539657593</v>
       </c>
       <c r="H2" t="n">
-        <v>18.00106239318848</v>
+        <v>14.52092909812927</v>
       </c>
       <c r="I2" t="n">
-        <v>14.64405751228333</v>
+        <v>13.26353287696838</v>
       </c>
       <c r="J2" t="n">
-        <v>15.4593141078949</v>
+        <v>15.45512652397156</v>
       </c>
       <c r="K2" t="n">
-        <v>15.34843516349792</v>
+        <v>12.56897258758545</v>
       </c>
       <c r="L2" t="n">
-        <v>15.15275979042053</v>
+        <v>14.36150529384613</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1999819278717</v>
+        <v>12.19741249084473</v>
       </c>
       <c r="C3" t="n">
-        <v>12.22717547416687</v>
+        <v>13.24062132835388</v>
       </c>
       <c r="D3" t="n">
-        <v>15.35858702659607</v>
+        <v>11.70085048675537</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92597079277039</v>
+        <v>17.48367738723755</v>
       </c>
       <c r="F3" t="n">
-        <v>18.29851889610291</v>
+        <v>12.09792566299438</v>
       </c>
       <c r="G3" t="n">
-        <v>12.82461953163147</v>
+        <v>16.95833659172058</v>
       </c>
       <c r="H3" t="n">
-        <v>15.80861639976501</v>
+        <v>15.43492364883423</v>
       </c>
       <c r="I3" t="n">
-        <v>14.86860847473145</v>
+        <v>11.56909108161926</v>
       </c>
       <c r="J3" t="n">
-        <v>15.70572996139526</v>
+        <v>11.98469662666321</v>
       </c>
       <c r="K3" t="n">
-        <v>12.09423112869263</v>
+        <v>15.92077732086182</v>
       </c>
       <c r="L3" t="n">
-        <v>14.33120396137238</v>
+        <v>13.8588312625885</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>13.43090867996216</v>
+        <v>17.43836665153503</v>
       </c>
       <c r="C4" t="n">
-        <v>13.60396575927734</v>
+        <v>16.0493335723877</v>
       </c>
       <c r="D4" t="n">
-        <v>12.94977688789368</v>
+        <v>12.46965336799622</v>
       </c>
       <c r="E4" t="n">
-        <v>16.95701813697815</v>
+        <v>14.36736559867859</v>
       </c>
       <c r="F4" t="n">
-        <v>17.44413280487061</v>
+        <v>12.55828166007996</v>
       </c>
       <c r="G4" t="n">
-        <v>12.51120734214783</v>
+        <v>18.35731887817383</v>
       </c>
       <c r="H4" t="n">
-        <v>13.36206769943237</v>
+        <v>13.00461506843567</v>
       </c>
       <c r="I4" t="n">
-        <v>14.94911479949951</v>
+        <v>12.78397297859192</v>
       </c>
       <c r="J4" t="n">
-        <v>13.31890201568604</v>
+        <v>17.30361843109131</v>
       </c>
       <c r="K4" t="n">
-        <v>13.64883804321289</v>
+        <v>12.1753671169281</v>
       </c>
       <c r="L4" t="n">
-        <v>14.21759321689606</v>
+        <v>14.65078933238983</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>14.40440893173218</v>
+        <v>11.34599542617798</v>
       </c>
       <c r="C5" t="n">
-        <v>13.8075590133667</v>
+        <v>16.57668447494507</v>
       </c>
       <c r="D5" t="n">
-        <v>13.02100539207458</v>
+        <v>11.73821330070496</v>
       </c>
       <c r="E5" t="n">
-        <v>11.91452074050903</v>
+        <v>11.23636865615845</v>
       </c>
       <c r="F5" t="n">
-        <v>11.6373131275177</v>
+        <v>17.15497064590454</v>
       </c>
       <c r="G5" t="n">
-        <v>14.052485704422</v>
+        <v>11.69173383712769</v>
       </c>
       <c r="H5" t="n">
-        <v>12.11738801002502</v>
+        <v>11.22099256515503</v>
       </c>
       <c r="I5" t="n">
-        <v>11.91984844207764</v>
+        <v>12.02135252952576</v>
       </c>
       <c r="J5" t="n">
-        <v>11.20236587524414</v>
+        <v>12.73034143447876</v>
       </c>
       <c r="K5" t="n">
-        <v>12.7412691116333</v>
+        <v>11.66683220863342</v>
       </c>
       <c r="L5" t="n">
-        <v>12.68181643486023</v>
+        <v>12.73834850788116</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>16.82549595832825</v>
+        <v>12.44578719139099</v>
       </c>
       <c r="C6" t="n">
-        <v>15.64394879341125</v>
+        <v>12.11465954780579</v>
       </c>
       <c r="D6" t="n">
-        <v>16.5683913230896</v>
+        <v>12.29483222961426</v>
       </c>
       <c r="E6" t="n">
-        <v>22.55164194107056</v>
+        <v>12.3917818069458</v>
       </c>
       <c r="F6" t="n">
-        <v>13.13536763191223</v>
+        <v>17.15989518165588</v>
       </c>
       <c r="G6" t="n">
-        <v>11.85946655273438</v>
+        <v>12.2944598197937</v>
       </c>
       <c r="H6" t="n">
-        <v>13.32293152809143</v>
+        <v>12.51556205749512</v>
       </c>
       <c r="I6" t="n">
-        <v>15.35443949699402</v>
+        <v>11.99894380569458</v>
       </c>
       <c r="J6" t="n">
-        <v>12.61880874633789</v>
+        <v>15.60142064094543</v>
       </c>
       <c r="K6" t="n">
-        <v>13.7487108707428</v>
+        <v>17.07006812095642</v>
       </c>
       <c r="L6" t="n">
-        <v>15.16292028427124</v>
+        <v>13.5887410402298</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>12.38369965553284</v>
+        <v>16.3434534072876</v>
       </c>
       <c r="C7" t="n">
-        <v>16.68808484077454</v>
+        <v>12.17456841468811</v>
       </c>
       <c r="D7" t="n">
-        <v>16.11687803268433</v>
+        <v>14.78264236450195</v>
       </c>
       <c r="E7" t="n">
-        <v>12.25206995010376</v>
+        <v>16.36563062667847</v>
       </c>
       <c r="F7" t="n">
-        <v>15.75655603408813</v>
+        <v>12.51583480834961</v>
       </c>
       <c r="G7" t="n">
-        <v>11.83421754837036</v>
+        <v>16.33536863327026</v>
       </c>
       <c r="H7" t="n">
-        <v>12.42403149604797</v>
+        <v>11.60396838188171</v>
       </c>
       <c r="I7" t="n">
-        <v>15.98693466186523</v>
+        <v>17.1883978843689</v>
       </c>
       <c r="J7" t="n">
-        <v>12.70681977272034</v>
+        <v>11.97250938415527</v>
       </c>
       <c r="K7" t="n">
-        <v>14.35177683830261</v>
+        <v>12.00586557388306</v>
       </c>
       <c r="L7" t="n">
-        <v>14.05010688304901</v>
+        <v>14.12882394790649</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>12.71794056892395</v>
+        <v>14.76037693023682</v>
       </c>
       <c r="C8" t="n">
-        <v>14.98395609855652</v>
+        <v>12.0338191986084</v>
       </c>
       <c r="D8" t="n">
-        <v>15.33593583106995</v>
+        <v>14.53990793228149</v>
       </c>
       <c r="E8" t="n">
-        <v>12.75465059280396</v>
+        <v>13.98311638832092</v>
       </c>
       <c r="F8" t="n">
-        <v>12.87088823318481</v>
+        <v>12.30878877639771</v>
       </c>
       <c r="G8" t="n">
-        <v>16.63601016998291</v>
+        <v>11.66581511497498</v>
       </c>
       <c r="H8" t="n">
-        <v>16.09595346450806</v>
+        <v>16.13761019706726</v>
       </c>
       <c r="I8" t="n">
-        <v>14.10088992118835</v>
+        <v>12.29702138900757</v>
       </c>
       <c r="J8" t="n">
-        <v>13.75742626190186</v>
+        <v>12.45002222061157</v>
       </c>
       <c r="K8" t="n">
-        <v>15.92183113098145</v>
+        <v>17.13708829879761</v>
       </c>
       <c r="L8" t="n">
-        <v>14.51754822731018</v>
+        <v>13.73135664463043</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43447589874268</v>
+        <v>12.02145481109619</v>
       </c>
       <c r="C9" t="n">
-        <v>12.23450899124146</v>
+        <v>11.64789533615112</v>
       </c>
       <c r="D9" t="n">
-        <v>12.20184183120728</v>
+        <v>13.5836193561554</v>
       </c>
       <c r="E9" t="n">
-        <v>15.51817679405212</v>
+        <v>11.41849732398987</v>
       </c>
       <c r="F9" t="n">
-        <v>17.67259550094604</v>
+        <v>11.03273677825928</v>
       </c>
       <c r="G9" t="n">
-        <v>13.75162887573242</v>
+        <v>18.09548902511597</v>
       </c>
       <c r="H9" t="n">
-        <v>16.57333755493164</v>
+        <v>13.65074062347412</v>
       </c>
       <c r="I9" t="n">
-        <v>13.63318634033203</v>
+        <v>15.61799335479736</v>
       </c>
       <c r="J9" t="n">
-        <v>16.89131307601929</v>
+        <v>17.40017247200012</v>
       </c>
       <c r="K9" t="n">
-        <v>14.24086308479309</v>
+        <v>11.49131441116333</v>
       </c>
       <c r="L9" t="n">
-        <v>14.51519279479981</v>
+        <v>13.59599134922028</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>12.34180474281311</v>
+        <v>12.07162570953369</v>
       </c>
       <c r="C10" t="n">
-        <v>12.31007528305054</v>
+        <v>13.09358096122742</v>
       </c>
       <c r="D10" t="n">
-        <v>13.01786017417908</v>
+        <v>12.73095488548279</v>
       </c>
       <c r="E10" t="n">
-        <v>14.77788209915161</v>
+        <v>12.01868081092834</v>
       </c>
       <c r="F10" t="n">
-        <v>15.14692187309265</v>
+        <v>11.51680779457092</v>
       </c>
       <c r="G10" t="n">
-        <v>15.93728256225586</v>
+        <v>13.68564343452454</v>
       </c>
       <c r="H10" t="n">
-        <v>15.26677203178406</v>
+        <v>15.9840247631073</v>
       </c>
       <c r="I10" t="n">
-        <v>13.10011744499207</v>
+        <v>12.36546158790588</v>
       </c>
       <c r="J10" t="n">
-        <v>13.9056179523468</v>
+        <v>12.96042633056641</v>
       </c>
       <c r="K10" t="n">
-        <v>13.78842544555664</v>
+        <v>14.7645161151886</v>
       </c>
       <c r="L10" t="n">
-        <v>13.95927596092224</v>
+        <v>13.11917223930359</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>15.67790913581848</v>
+        <v>12.31606411933899</v>
       </c>
       <c r="C11" t="n">
-        <v>14.54065537452698</v>
+        <v>17.8132016658783</v>
       </c>
       <c r="D11" t="n">
-        <v>15.60104632377625</v>
+        <v>14.71408104896545</v>
       </c>
       <c r="E11" t="n">
-        <v>15.940434217453</v>
+        <v>12.75031065940857</v>
       </c>
       <c r="F11" t="n">
-        <v>15.68889498710632</v>
+        <v>15.39465832710266</v>
       </c>
       <c r="G11" t="n">
-        <v>12.8090648651123</v>
+        <v>12.47863054275513</v>
       </c>
       <c r="H11" t="n">
-        <v>14.8900580406189</v>
+        <v>18.08296799659729</v>
       </c>
       <c r="I11" t="n">
-        <v>14.21012306213379</v>
+        <v>12.79894161224365</v>
       </c>
       <c r="J11" t="n">
-        <v>14.06288480758667</v>
+        <v>12.89555788040161</v>
       </c>
       <c r="K11" t="n">
-        <v>12.39697051048279</v>
+        <v>16.06272196769714</v>
       </c>
       <c r="L11" t="n">
-        <v>14.58180413246155</v>
+        <v>14.53071358203888</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>16.80696201324463</v>
+        <v>13.92001295089722</v>
       </c>
       <c r="C12" t="n">
-        <v>13.17381191253662</v>
+        <v>13.13871431350708</v>
       </c>
       <c r="D12" t="n">
-        <v>14.53048133850098</v>
+        <v>16.18974137306213</v>
       </c>
       <c r="E12" t="n">
-        <v>13.35796546936035</v>
+        <v>19.50158739089966</v>
       </c>
       <c r="F12" t="n">
-        <v>16.21289253234863</v>
+        <v>18.10222935676575</v>
       </c>
       <c r="G12" t="n">
-        <v>14.63996076583862</v>
+        <v>15.19937920570374</v>
       </c>
       <c r="H12" t="n">
-        <v>14.31641221046448</v>
+        <v>16.83929514884949</v>
       </c>
       <c r="I12" t="n">
-        <v>17.36870050430298</v>
+        <v>16.97320055961609</v>
       </c>
       <c r="J12" t="n">
-        <v>15.50947856903076</v>
+        <v>15.82586240768433</v>
       </c>
       <c r="K12" t="n">
-        <v>14.18457674980164</v>
+        <v>16.66466808319092</v>
       </c>
       <c r="L12" t="n">
-        <v>15.01012420654297</v>
+        <v>16.23546907901764</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>13.9919605255127</v>
+        <v>16.46348690986633</v>
       </c>
       <c r="C13" t="n">
-        <v>16.32745981216431</v>
+        <v>18.01602554321289</v>
       </c>
       <c r="D13" t="n">
-        <v>20.15688467025757</v>
+        <v>15.78562331199646</v>
       </c>
       <c r="E13" t="n">
-        <v>13.59982752799988</v>
+        <v>15.67551183700562</v>
       </c>
       <c r="F13" t="n">
-        <v>18.4181272983551</v>
+        <v>19.62754249572754</v>
       </c>
       <c r="G13" t="n">
-        <v>14.15216708183289</v>
+        <v>15.55457091331482</v>
       </c>
       <c r="H13" t="n">
-        <v>13.489009141922</v>
+        <v>13.82489275932312</v>
       </c>
       <c r="I13" t="n">
-        <v>13.53947162628174</v>
+        <v>14.33221578598022</v>
       </c>
       <c r="J13" t="n">
-        <v>13.62890696525574</v>
+        <v>14.01467180252075</v>
       </c>
       <c r="K13" t="n">
-        <v>13.61891961097717</v>
+        <v>13.82530188560486</v>
       </c>
       <c r="L13" t="n">
-        <v>15.09227342605591</v>
+        <v>15.71198432445526</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>15.31279850006104</v>
+        <v>12.56014728546143</v>
       </c>
       <c r="C14" t="n">
-        <v>13.34365749359131</v>
+        <v>12.50260734558105</v>
       </c>
       <c r="D14" t="n">
-        <v>16.239497423172</v>
+        <v>12.96890258789062</v>
       </c>
       <c r="E14" t="n">
-        <v>11.64212489128113</v>
+        <v>12.96942210197449</v>
       </c>
       <c r="F14" t="n">
-        <v>15.62718558311462</v>
+        <v>17.21632027626038</v>
       </c>
       <c r="G14" t="n">
-        <v>15.44316983222961</v>
+        <v>14.63993430137634</v>
       </c>
       <c r="H14" t="n">
-        <v>13.35324025154114</v>
+        <v>15.69455933570862</v>
       </c>
       <c r="I14" t="n">
-        <v>17.9966025352478</v>
+        <v>18.85777282714844</v>
       </c>
       <c r="J14" t="n">
-        <v>14.58867430686951</v>
+        <v>17.34510254859924</v>
       </c>
       <c r="K14" t="n">
-        <v>14.11406350135803</v>
+        <v>13.44145274162292</v>
       </c>
       <c r="L14" t="n">
-        <v>14.76610143184662</v>
+        <v>14.81962213516235</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>16.01105976104736</v>
+        <v>12.7344753742218</v>
       </c>
       <c r="C15" t="n">
-        <v>18.83424615859985</v>
+        <v>15.83094954490662</v>
       </c>
       <c r="D15" t="n">
-        <v>15.71614146232605</v>
+        <v>11.18756079673767</v>
       </c>
       <c r="E15" t="n">
-        <v>15.3725950717926</v>
+        <v>12.92266845703125</v>
       </c>
       <c r="F15" t="n">
-        <v>15.6109983921051</v>
+        <v>16.23150444030762</v>
       </c>
       <c r="G15" t="n">
-        <v>12.13500642776489</v>
+        <v>14.68648028373718</v>
       </c>
       <c r="H15" t="n">
-        <v>16.72779321670532</v>
+        <v>14.7455267906189</v>
       </c>
       <c r="I15" t="n">
-        <v>12.7568621635437</v>
+        <v>16.72376370429993</v>
       </c>
       <c r="J15" t="n">
-        <v>12.06231355667114</v>
+        <v>15.82173371315002</v>
       </c>
       <c r="K15" t="n">
-        <v>14.66684889793396</v>
+        <v>14.19013667106628</v>
       </c>
       <c r="L15" t="n">
-        <v>14.989386510849</v>
+        <v>14.50747997760773</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>17.30358600616455</v>
+        <v>11.72739386558533</v>
       </c>
       <c r="C16" t="n">
-        <v>14.97911286354065</v>
+        <v>17.73000168800354</v>
       </c>
       <c r="D16" t="n">
-        <v>16.24901437759399</v>
+        <v>12.84265613555908</v>
       </c>
       <c r="E16" t="n">
-        <v>15.97331714630127</v>
+        <v>16.91824984550476</v>
       </c>
       <c r="F16" t="n">
-        <v>15.52577495574951</v>
+        <v>14.49427461624146</v>
       </c>
       <c r="G16" t="n">
-        <v>14.40857028961182</v>
+        <v>18.40062832832336</v>
       </c>
       <c r="H16" t="n">
-        <v>14.36312985420227</v>
+        <v>12.45774388313293</v>
       </c>
       <c r="I16" t="n">
-        <v>13.82924127578735</v>
+        <v>13.04944181442261</v>
       </c>
       <c r="J16" t="n">
-        <v>14.33437728881836</v>
+        <v>12.5046021938324</v>
       </c>
       <c r="K16" t="n">
-        <v>15.60378527641296</v>
+        <v>16.28196811676025</v>
       </c>
       <c r="L16" t="n">
-        <v>15.25699093341827</v>
+        <v>14.64069604873657</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>11.90188002586365</v>
+        <v>12.82097768783569</v>
       </c>
       <c r="C17" t="n">
-        <v>15.60796046257019</v>
+        <v>12.72656154632568</v>
       </c>
       <c r="D17" t="n">
-        <v>11.97896099090576</v>
+        <v>14.76972055435181</v>
       </c>
       <c r="E17" t="n">
-        <v>15.42785143852234</v>
+        <v>16.50641512870789</v>
       </c>
       <c r="F17" t="n">
-        <v>15.87507224082947</v>
+        <v>12.28838419914246</v>
       </c>
       <c r="G17" t="n">
-        <v>16.00611972808838</v>
+        <v>14.78847694396973</v>
       </c>
       <c r="H17" t="n">
-        <v>12.58405375480652</v>
+        <v>12.92847800254822</v>
       </c>
       <c r="I17" t="n">
-        <v>16.20595002174377</v>
+        <v>11.54229807853699</v>
       </c>
       <c r="J17" t="n">
-        <v>14.64779019355774</v>
+        <v>11.60301566123962</v>
       </c>
       <c r="K17" t="n">
-        <v>16.17967367172241</v>
+        <v>15.78977537155151</v>
       </c>
       <c r="L17" t="n">
-        <v>14.64153125286102</v>
+        <v>13.57641031742096</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>11.99242568016052</v>
+        <v>16.70579838752747</v>
       </c>
       <c r="C18" t="n">
-        <v>12.4080958366394</v>
+        <v>21.05191802978516</v>
       </c>
       <c r="D18" t="n">
-        <v>16.57792639732361</v>
+        <v>14.54147052764893</v>
       </c>
       <c r="E18" t="n">
-        <v>12.83658599853516</v>
+        <v>16.7344982624054</v>
       </c>
       <c r="F18" t="n">
-        <v>11.46084380149841</v>
+        <v>12.62723159790039</v>
       </c>
       <c r="G18" t="n">
-        <v>12.47575807571411</v>
+        <v>15.82168984413147</v>
       </c>
       <c r="H18" t="n">
-        <v>12.76989817619324</v>
+        <v>12.59332203865051</v>
       </c>
       <c r="I18" t="n">
-        <v>11.80207991600037</v>
+        <v>17.28388142585754</v>
       </c>
       <c r="J18" t="n">
-        <v>12.78725957870483</v>
+        <v>11.57020735740662</v>
       </c>
       <c r="K18" t="n">
-        <v>14.42436718940735</v>
+        <v>12.82809352874756</v>
       </c>
       <c r="L18" t="n">
-        <v>12.9535240650177</v>
+        <v>15.1758111000061</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22664356231689</v>
+        <v>15.83008241653442</v>
       </c>
       <c r="C19" t="n">
-        <v>13.96458196640015</v>
+        <v>16.82423138618469</v>
       </c>
       <c r="D19" t="n">
-        <v>11.75784134864807</v>
+        <v>12.20540285110474</v>
       </c>
       <c r="E19" t="n">
-        <v>15.27770638465881</v>
+        <v>12.27351856231689</v>
       </c>
       <c r="F19" t="n">
-        <v>13.96590995788574</v>
+        <v>14.08038449287415</v>
       </c>
       <c r="G19" t="n">
-        <v>13.60560178756714</v>
+        <v>14.29198932647705</v>
       </c>
       <c r="H19" t="n">
-        <v>15.52856373786926</v>
+        <v>15.62996864318848</v>
       </c>
       <c r="I19" t="n">
-        <v>12.00777959823608</v>
+        <v>13.17594146728516</v>
       </c>
       <c r="J19" t="n">
-        <v>13.18306088447571</v>
+        <v>16.68692898750305</v>
       </c>
       <c r="K19" t="n">
-        <v>11.98025441169739</v>
+        <v>18.36743497848511</v>
       </c>
       <c r="L19" t="n">
-        <v>13.34979436397552</v>
+        <v>14.93658831119537</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>14.10193252563477</v>
+        <v>15.92873477935791</v>
       </c>
       <c r="C20" t="n">
-        <v>14.55912828445435</v>
+        <v>13.01958727836609</v>
       </c>
       <c r="D20" t="n">
-        <v>14.39521932601929</v>
+        <v>17.12838673591614</v>
       </c>
       <c r="E20" t="n">
-        <v>14.12926506996155</v>
+        <v>16.67853784561157</v>
       </c>
       <c r="F20" t="n">
-        <v>15.40418171882629</v>
+        <v>14.60497736930847</v>
       </c>
       <c r="G20" t="n">
-        <v>15.01282644271851</v>
+        <v>13.64387917518616</v>
       </c>
       <c r="H20" t="n">
-        <v>15.30549836158752</v>
+        <v>15.63190531730652</v>
       </c>
       <c r="I20" t="n">
-        <v>11.36849474906921</v>
+        <v>14.46682119369507</v>
       </c>
       <c r="J20" t="n">
-        <v>12.57183861732483</v>
+        <v>16.74013900756836</v>
       </c>
       <c r="K20" t="n">
-        <v>14.79000878334045</v>
+        <v>13.6163489818573</v>
       </c>
       <c r="L20" t="n">
-        <v>14.16383938789368</v>
+        <v>15.14593176841736</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>11.5419008731842</v>
+        <v>12.96708059310913</v>
       </c>
       <c r="C21" t="n">
-        <v>10.43362998962402</v>
+        <v>12.26131772994995</v>
       </c>
       <c r="D21" t="n">
-        <v>14.94095993041992</v>
+        <v>13.84367084503174</v>
       </c>
       <c r="E21" t="n">
-        <v>12.30891799926758</v>
+        <v>12.30038523674011</v>
       </c>
       <c r="F21" t="n">
-        <v>17.66162085533142</v>
+        <v>13.8529942035675</v>
       </c>
       <c r="G21" t="n">
-        <v>11.67312240600586</v>
+        <v>12.852135181427</v>
       </c>
       <c r="H21" t="n">
-        <v>11.69137096405029</v>
+        <v>11.88229656219482</v>
       </c>
       <c r="I21" t="n">
-        <v>14.8124885559082</v>
+        <v>13.93373870849609</v>
       </c>
       <c r="J21" t="n">
-        <v>12.57031559944153</v>
+        <v>15.91072702407837</v>
       </c>
       <c r="K21" t="n">
-        <v>10.70317411422729</v>
+        <v>12.21879172325134</v>
       </c>
       <c r="L21" t="n">
-        <v>12.83375012874603</v>
+        <v>13.20231378078461</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>14.84903335571289</v>
+        <v>19.7246675491333</v>
       </c>
       <c r="C22" t="n">
-        <v>12.08634662628174</v>
+        <v>12.11118054389954</v>
       </c>
       <c r="D22" t="n">
-        <v>15.79068803787231</v>
+        <v>14.59268856048584</v>
       </c>
       <c r="E22" t="n">
-        <v>13.49316668510437</v>
+        <v>12.08148074150085</v>
       </c>
       <c r="F22" t="n">
-        <v>13.35922050476074</v>
+        <v>17.32205653190613</v>
       </c>
       <c r="G22" t="n">
-        <v>14.41059613227844</v>
+        <v>18.2998833656311</v>
       </c>
       <c r="H22" t="n">
-        <v>16.59298920631409</v>
+        <v>15.58292698860168</v>
       </c>
       <c r="I22" t="n">
-        <v>13.62163066864014</v>
+        <v>13.36737012863159</v>
       </c>
       <c r="J22" t="n">
-        <v>13.17066788673401</v>
+        <v>19.02677536010742</v>
       </c>
       <c r="K22" t="n">
-        <v>16.67064094543457</v>
+        <v>15.61246943473816</v>
       </c>
       <c r="L22" t="n">
-        <v>14.40449800491333</v>
+        <v>15.77214992046356</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>13.95125722885132</v>
+        <v>14.8014178276062</v>
       </c>
       <c r="C23" t="n">
-        <v>11.98110055923462</v>
+        <v>18.12144112586975</v>
       </c>
       <c r="D23" t="n">
-        <v>11.7111120223999</v>
+        <v>13.59345245361328</v>
       </c>
       <c r="E23" t="n">
-        <v>14.6174955368042</v>
+        <v>12.23062443733215</v>
       </c>
       <c r="F23" t="n">
-        <v>11.93254446983337</v>
+        <v>12.06373858451843</v>
       </c>
       <c r="G23" t="n">
-        <v>13.33699774742126</v>
+        <v>15.69940257072449</v>
       </c>
       <c r="H23" t="n">
-        <v>13.36794471740723</v>
+        <v>13.66545557975769</v>
       </c>
       <c r="I23" t="n">
-        <v>15.3498547077179</v>
+        <v>12.36471152305603</v>
       </c>
       <c r="J23" t="n">
-        <v>11.20020723342896</v>
+        <v>12.2733371257782</v>
       </c>
       <c r="K23" t="n">
-        <v>15.25780820846558</v>
+        <v>11.99912524223328</v>
       </c>
       <c r="L23" t="n">
-        <v>13.27063224315643</v>
+        <v>13.68127064704895</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>13.81581854820251</v>
+        <v>16.93392586708069</v>
       </c>
       <c r="C24" t="n">
-        <v>14.95143342018127</v>
+        <v>11.73366618156433</v>
       </c>
       <c r="D24" t="n">
-        <v>15.97579956054688</v>
+        <v>13.28988456726074</v>
       </c>
       <c r="E24" t="n">
-        <v>14.26117563247681</v>
+        <v>13.11831450462341</v>
       </c>
       <c r="F24" t="n">
-        <v>13.38244318962097</v>
+        <v>13.04115557670593</v>
       </c>
       <c r="G24" t="n">
-        <v>14.28535342216492</v>
+        <v>14.59709572792053</v>
       </c>
       <c r="H24" t="n">
-        <v>18.54752278327942</v>
+        <v>15.2724072933197</v>
       </c>
       <c r="I24" t="n">
-        <v>16.61409974098206</v>
+        <v>12.77922129631042</v>
       </c>
       <c r="J24" t="n">
-        <v>13.65974974632263</v>
+        <v>12.54716062545776</v>
       </c>
       <c r="K24" t="n">
-        <v>18.32781434059143</v>
+        <v>16.32338166236877</v>
       </c>
       <c r="L24" t="n">
-        <v>15.38212103843689</v>
+        <v>13.96362133026123</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>17.39200687408447</v>
+        <v>20.01347970962524</v>
       </c>
       <c r="C25" t="n">
-        <v>15.25196433067322</v>
+        <v>15.01783919334412</v>
       </c>
       <c r="D25" t="n">
-        <v>13.78927135467529</v>
+        <v>18.53267049789429</v>
       </c>
       <c r="E25" t="n">
-        <v>16.46871733665466</v>
+        <v>16.23813199996948</v>
       </c>
       <c r="F25" t="n">
-        <v>17.60170602798462</v>
+        <v>23.423171043396</v>
       </c>
       <c r="G25" t="n">
-        <v>14.62353992462158</v>
+        <v>19.22059965133667</v>
       </c>
       <c r="H25" t="n">
-        <v>14.60083484649658</v>
+        <v>21.72590041160583</v>
       </c>
       <c r="I25" t="n">
-        <v>21.19772481918335</v>
+        <v>14.69370627403259</v>
       </c>
       <c r="J25" t="n">
-        <v>14.26679468154907</v>
+        <v>25.0709547996521</v>
       </c>
       <c r="K25" t="n">
-        <v>15.16695928573608</v>
+        <v>20.68568253517151</v>
       </c>
       <c r="L25" t="n">
-        <v>16.03595194816589</v>
+        <v>19.46221361160278</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>12.93293452262878</v>
+        <v>12.33401584625244</v>
       </c>
       <c r="C26" t="n">
-        <v>14.48869705200195</v>
+        <v>12.98627185821533</v>
       </c>
       <c r="D26" t="n">
-        <v>13.89271092414856</v>
+        <v>11.83235764503479</v>
       </c>
       <c r="E26" t="n">
-        <v>13.35939192771912</v>
+        <v>11.55410146713257</v>
       </c>
       <c r="F26" t="n">
-        <v>11.88231730461121</v>
+        <v>10.12094283103943</v>
       </c>
       <c r="G26" t="n">
-        <v>11.86698317527771</v>
+        <v>10.64852356910706</v>
       </c>
       <c r="H26" t="n">
-        <v>11.61684203147888</v>
+        <v>10.36727619171143</v>
       </c>
       <c r="I26" t="n">
-        <v>12.43633198738098</v>
+        <v>13.70634627342224</v>
       </c>
       <c r="J26" t="n">
-        <v>13.50201153755188</v>
+        <v>10.88659882545471</v>
       </c>
       <c r="K26" t="n">
-        <v>12.46683955192566</v>
+        <v>14.21799993515015</v>
       </c>
       <c r="L26" t="n">
-        <v>12.84450600147247</v>
+        <v>11.86544344425201</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>13.56837177276611</v>
+        <v>14.63264799118042</v>
       </c>
       <c r="C27" t="n">
-        <v>14.29361605644226</v>
+        <v>14.72462296485901</v>
       </c>
       <c r="D27" t="n">
-        <v>17.59676837921143</v>
+        <v>15.10716652870178</v>
       </c>
       <c r="E27" t="n">
-        <v>12.80157446861267</v>
+        <v>12.41321015357971</v>
       </c>
       <c r="F27" t="n">
-        <v>12.16009187698364</v>
+        <v>12.75846266746521</v>
       </c>
       <c r="G27" t="n">
-        <v>12.79892921447754</v>
+        <v>14.30030632019043</v>
       </c>
       <c r="H27" t="n">
-        <v>16.6929075717926</v>
+        <v>15.96729803085327</v>
       </c>
       <c r="I27" t="n">
-        <v>16.29044699668884</v>
+        <v>12.39600324630737</v>
       </c>
       <c r="J27" t="n">
-        <v>14.4605815410614</v>
+        <v>14.88904762268066</v>
       </c>
       <c r="K27" t="n">
-        <v>17.73858571052551</v>
+        <v>13.97790884971619</v>
       </c>
       <c r="L27" t="n">
-        <v>14.8401873588562</v>
+        <v>14.11666743755341</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>14.65896153450012</v>
+        <v>17.30047798156738</v>
       </c>
       <c r="C28" t="n">
-        <v>12.32417488098145</v>
+        <v>12.68755197525024</v>
       </c>
       <c r="D28" t="n">
-        <v>12.50658440589905</v>
+        <v>11.49646091461182</v>
       </c>
       <c r="E28" t="n">
-        <v>16.14192175865173</v>
+        <v>11.27894711494446</v>
       </c>
       <c r="F28" t="n">
-        <v>13.32085037231445</v>
+        <v>13.20231938362122</v>
       </c>
       <c r="G28" t="n">
-        <v>15.11783003807068</v>
+        <v>13.68250060081482</v>
       </c>
       <c r="H28" t="n">
-        <v>13.38788247108459</v>
+        <v>13.18136286735535</v>
       </c>
       <c r="I28" t="n">
-        <v>14.2485146522522</v>
+        <v>13.24245738983154</v>
       </c>
       <c r="J28" t="n">
-        <v>13.09898519515991</v>
+        <v>14.12938284873962</v>
       </c>
       <c r="K28" t="n">
-        <v>14.281977891922</v>
+        <v>13.98963260650635</v>
       </c>
       <c r="L28" t="n">
-        <v>13.90876832008362</v>
+        <v>13.41910936832428</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>12.56405186653137</v>
+        <v>11.59698724746704</v>
       </c>
       <c r="C29" t="n">
-        <v>16.89758896827698</v>
+        <v>12.28856420516968</v>
       </c>
       <c r="D29" t="n">
-        <v>15.58030843734741</v>
+        <v>14.97952890396118</v>
       </c>
       <c r="E29" t="n">
-        <v>17.41475033760071</v>
+        <v>12.35799837112427</v>
       </c>
       <c r="F29" t="n">
-        <v>16.8388466835022</v>
+        <v>11.43036389350891</v>
       </c>
       <c r="G29" t="n">
-        <v>12.94871234893799</v>
+        <v>11.11231279373169</v>
       </c>
       <c r="H29" t="n">
-        <v>15.76950526237488</v>
+        <v>14.02207851409912</v>
       </c>
       <c r="I29" t="n">
-        <v>13.06133532524109</v>
+        <v>10.62534189224243</v>
       </c>
       <c r="J29" t="n">
-        <v>17.83695936203003</v>
+        <v>11.54077696800232</v>
       </c>
       <c r="K29" t="n">
-        <v>11.62458896636963</v>
+        <v>10.73587656021118</v>
       </c>
       <c r="L29" t="n">
-        <v>15.05366475582123</v>
+        <v>12.06898293495178</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>16.18302130699158</v>
+        <v>17.05419993400574</v>
       </c>
       <c r="C30" t="n">
-        <v>15.5232253074646</v>
+        <v>12.18747615814209</v>
       </c>
       <c r="D30" t="n">
-        <v>12.58764505386353</v>
+        <v>15.33552289009094</v>
       </c>
       <c r="E30" t="n">
-        <v>15.29361748695374</v>
+        <v>14.1777400970459</v>
       </c>
       <c r="F30" t="n">
-        <v>15.18550586700439</v>
+        <v>14.71181511878967</v>
       </c>
       <c r="G30" t="n">
-        <v>12.41230344772339</v>
+        <v>19.18863606452942</v>
       </c>
       <c r="H30" t="n">
-        <v>13.17945981025696</v>
+        <v>16.79974961280823</v>
       </c>
       <c r="I30" t="n">
-        <v>11.76921606063843</v>
+        <v>12.50655078887939</v>
       </c>
       <c r="J30" t="n">
-        <v>12.46400785446167</v>
+        <v>12.93901634216309</v>
       </c>
       <c r="K30" t="n">
-        <v>12.43907499313354</v>
+        <v>16.99732518196106</v>
       </c>
       <c r="L30" t="n">
-        <v>13.70370771884918</v>
+        <v>15.18980321884155</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>15.58921504020691</v>
+        <v>16.7921462059021</v>
       </c>
       <c r="C31" t="n">
-        <v>15.55585646629333</v>
+        <v>18.59797835350037</v>
       </c>
       <c r="D31" t="n">
-        <v>14.7501118183136</v>
+        <v>15.4726231098175</v>
       </c>
       <c r="E31" t="n">
-        <v>13.29716825485229</v>
+        <v>15.57362246513367</v>
       </c>
       <c r="F31" t="n">
-        <v>15.46490883827209</v>
+        <v>17.3018810749054</v>
       </c>
       <c r="G31" t="n">
-        <v>13.68624782562256</v>
+        <v>14.98576188087463</v>
       </c>
       <c r="H31" t="n">
-        <v>13.54083824157715</v>
+        <v>13.42163014411926</v>
       </c>
       <c r="I31" t="n">
-        <v>12.01609325408936</v>
+        <v>15.38798952102661</v>
       </c>
       <c r="J31" t="n">
-        <v>16.66385364532471</v>
+        <v>12.37734341621399</v>
       </c>
       <c r="K31" t="n">
-        <v>15.83800935745239</v>
+        <v>12.56597304344177</v>
       </c>
       <c r="L31" t="n">
-        <v>14.64023027420044</v>
+        <v>15.24769492149353</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>15.57257604598999</v>
+        <v>12.50145792961121</v>
       </c>
       <c r="C32" t="n">
-        <v>11.632084608078</v>
+        <v>14.78147506713867</v>
       </c>
       <c r="D32" t="n">
-        <v>12.81905031204224</v>
+        <v>12.57424139976501</v>
       </c>
       <c r="E32" t="n">
-        <v>16.23427724838257</v>
+        <v>12.21253752708435</v>
       </c>
       <c r="F32" t="n">
-        <v>11.66846799850464</v>
+        <v>12.44175696372986</v>
       </c>
       <c r="G32" t="n">
-        <v>13.07331252098083</v>
+        <v>14.17509341239929</v>
       </c>
       <c r="H32" t="n">
-        <v>16.53213620185852</v>
+        <v>17.00772333145142</v>
       </c>
       <c r="I32" t="n">
-        <v>11.96505737304688</v>
+        <v>12.38288521766663</v>
       </c>
       <c r="J32" t="n">
-        <v>15.79074597358704</v>
+        <v>12.04488563537598</v>
       </c>
       <c r="K32" t="n">
-        <v>14.56742310523987</v>
+        <v>14.7600040435791</v>
       </c>
       <c r="L32" t="n">
-        <v>13.98551313877106</v>
+        <v>13.48820605278015</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>17.05721163749695</v>
+        <v>12.76149702072144</v>
       </c>
       <c r="C33" t="n">
-        <v>15.22478771209717</v>
+        <v>12.51426553726196</v>
       </c>
       <c r="D33" t="n">
-        <v>15.58768343925476</v>
+        <v>17.65411067008972</v>
       </c>
       <c r="E33" t="n">
-        <v>15.51169228553772</v>
+        <v>16.01558780670166</v>
       </c>
       <c r="F33" t="n">
-        <v>14.36659240722656</v>
+        <v>12.91703033447266</v>
       </c>
       <c r="G33" t="n">
-        <v>14.65755414962769</v>
+        <v>13.20468759536743</v>
       </c>
       <c r="H33" t="n">
-        <v>12.2469277381897</v>
+        <v>13.47396802902222</v>
       </c>
       <c r="I33" t="n">
-        <v>15.76659536361694</v>
+        <v>14.69416379928589</v>
       </c>
       <c r="J33" t="n">
-        <v>13.39589905738831</v>
+        <v>16.85445332527161</v>
       </c>
       <c r="K33" t="n">
-        <v>14.47113943099976</v>
+        <v>16.90262913703918</v>
       </c>
       <c r="L33" t="n">
-        <v>14.82860832214356</v>
+        <v>14.69923932552338</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>14.54579257965088</v>
+        <v>11.23943877220154</v>
       </c>
       <c r="C34" t="n">
-        <v>11.49419450759888</v>
+        <v>10.9668755531311</v>
       </c>
       <c r="D34" t="n">
-        <v>14.1225438117981</v>
+        <v>12.42776584625244</v>
       </c>
       <c r="E34" t="n">
-        <v>10.61092591285706</v>
+        <v>11.59399509429932</v>
       </c>
       <c r="F34" t="n">
-        <v>15.13416528701782</v>
+        <v>11.99138450622559</v>
       </c>
       <c r="G34" t="n">
-        <v>10.7255756855011</v>
+        <v>12.60827255249023</v>
       </c>
       <c r="H34" t="n">
-        <v>14.39954543113708</v>
+        <v>11.93307042121887</v>
       </c>
       <c r="I34" t="n">
-        <v>11.41679453849792</v>
+        <v>12.3391478061676</v>
       </c>
       <c r="J34" t="n">
-        <v>10.89915537834167</v>
+        <v>11.37688255310059</v>
       </c>
       <c r="K34" t="n">
-        <v>11.59947657585144</v>
+        <v>10.97183799743652</v>
       </c>
       <c r="L34" t="n">
-        <v>12.49481697082519</v>
+        <v>11.74486711025238</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>12.34102869033813</v>
+        <v>17.7509777545929</v>
       </c>
       <c r="C35" t="n">
-        <v>13.11309313774109</v>
+        <v>17.66435408592224</v>
       </c>
       <c r="D35" t="n">
-        <v>12.567049741745</v>
+        <v>17.1386296749115</v>
       </c>
       <c r="E35" t="n">
-        <v>11.85278940200806</v>
+        <v>17.6004753112793</v>
       </c>
       <c r="F35" t="n">
-        <v>16.35999441146851</v>
+        <v>18.64391469955444</v>
       </c>
       <c r="G35" t="n">
-        <v>14.72617363929749</v>
+        <v>12.99743390083313</v>
       </c>
       <c r="H35" t="n">
-        <v>15.24935388565063</v>
+        <v>13.93148970603943</v>
       </c>
       <c r="I35" t="n">
-        <v>13.02711606025696</v>
+        <v>11.98295521736145</v>
       </c>
       <c r="J35" t="n">
-        <v>17.09206175804138</v>
+        <v>11.91440081596375</v>
       </c>
       <c r="K35" t="n">
-        <v>13.22659754753113</v>
+        <v>14.23198509216309</v>
       </c>
       <c r="L35" t="n">
-        <v>13.95552582740784</v>
+        <v>15.38566162586212</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>12.74733662605286</v>
+        <v>13.04060554504395</v>
       </c>
       <c r="C36" t="n">
-        <v>13.09093952178955</v>
+        <v>11.42515635490417</v>
       </c>
       <c r="D36" t="n">
-        <v>13.63325524330139</v>
+        <v>14.98991417884827</v>
       </c>
       <c r="E36" t="n">
-        <v>13.23777866363525</v>
+        <v>11.4655978679657</v>
       </c>
       <c r="F36" t="n">
-        <v>14.18436527252197</v>
+        <v>12.54746913909912</v>
       </c>
       <c r="G36" t="n">
-        <v>14.33498740196228</v>
+        <v>13.00291800498962</v>
       </c>
       <c r="H36" t="n">
-        <v>11.90219974517822</v>
+        <v>13.4391975402832</v>
       </c>
       <c r="I36" t="n">
-        <v>18.23251962661743</v>
+        <v>11.64846968650818</v>
       </c>
       <c r="J36" t="n">
-        <v>12.68667531013489</v>
+        <v>13.16089415550232</v>
       </c>
       <c r="K36" t="n">
-        <v>11.882239818573</v>
+        <v>15.84205102920532</v>
       </c>
       <c r="L36" t="n">
-        <v>13.59322972297668</v>
+        <v>13.05622735023499</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>12.70813679695129</v>
+        <v>11.67205381393433</v>
       </c>
       <c r="C37" t="n">
-        <v>17.34233474731445</v>
+        <v>16.56941938400269</v>
       </c>
       <c r="D37" t="n">
-        <v>12.11365437507629</v>
+        <v>16.92474007606506</v>
       </c>
       <c r="E37" t="n">
-        <v>11.88608765602112</v>
+        <v>13.96753072738647</v>
       </c>
       <c r="F37" t="n">
-        <v>11.64320707321167</v>
+        <v>15.20818257331848</v>
       </c>
       <c r="G37" t="n">
-        <v>12.82711362838745</v>
+        <v>12.04486584663391</v>
       </c>
       <c r="H37" t="n">
-        <v>14.6688289642334</v>
+        <v>12.04279518127441</v>
       </c>
       <c r="I37" t="n">
-        <v>12.93282413482666</v>
+        <v>12.0693507194519</v>
       </c>
       <c r="J37" t="n">
-        <v>12.78817439079285</v>
+        <v>11.40542197227478</v>
       </c>
       <c r="K37" t="n">
-        <v>15.12212228775024</v>
+        <v>19.03635501861572</v>
       </c>
       <c r="L37" t="n">
-        <v>13.40324840545654</v>
+        <v>14.09407153129578</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>11.88112950325012</v>
+        <v>14.65926170349121</v>
       </c>
       <c r="C38" t="n">
-        <v>12.20522904396057</v>
+        <v>15.03620409965515</v>
       </c>
       <c r="D38" t="n">
-        <v>16.69254183769226</v>
+        <v>18.4319052696228</v>
       </c>
       <c r="E38" t="n">
-        <v>15.21143221855164</v>
+        <v>15.49162411689758</v>
       </c>
       <c r="F38" t="n">
-        <v>12.49198722839355</v>
+        <v>11.36760067939758</v>
       </c>
       <c r="G38" t="n">
-        <v>12.73433756828308</v>
+        <v>12.28366112709045</v>
       </c>
       <c r="H38" t="n">
-        <v>15.19294261932373</v>
+        <v>15.76178169250488</v>
       </c>
       <c r="I38" t="n">
-        <v>15.99618411064148</v>
+        <v>13.25982570648193</v>
       </c>
       <c r="J38" t="n">
-        <v>12.60593152046204</v>
+        <v>15.3418447971344</v>
       </c>
       <c r="K38" t="n">
-        <v>13.10036635398865</v>
+        <v>12.75597381591797</v>
       </c>
       <c r="L38" t="n">
-        <v>13.81120820045471</v>
+        <v>14.4389683008194</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>9.843379497528076</v>
+        <v>11.22827410697937</v>
       </c>
       <c r="C39" t="n">
-        <v>12.09748935699463</v>
+        <v>12.06610202789307</v>
       </c>
       <c r="D39" t="n">
-        <v>11.74334311485291</v>
+        <v>10.92734527587891</v>
       </c>
       <c r="E39" t="n">
-        <v>13.35747861862183</v>
+        <v>12.00127983093262</v>
       </c>
       <c r="F39" t="n">
-        <v>13.17592620849609</v>
+        <v>10.85282421112061</v>
       </c>
       <c r="G39" t="n">
-        <v>13.67068815231323</v>
+        <v>13.1630699634552</v>
       </c>
       <c r="H39" t="n">
-        <v>14.64480590820312</v>
+        <v>17.19553208351135</v>
       </c>
       <c r="I39" t="n">
-        <v>12.78077960014343</v>
+        <v>11.43693542480469</v>
       </c>
       <c r="J39" t="n">
-        <v>10.6715714931488</v>
+        <v>13.43290209770203</v>
       </c>
       <c r="K39" t="n">
-        <v>15.98202514648438</v>
+        <v>10.91456818580627</v>
       </c>
       <c r="L39" t="n">
-        <v>12.79674870967865</v>
+        <v>12.32188332080841</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>16.12808799743652</v>
+        <v>14.81477689743042</v>
       </c>
       <c r="C40" t="n">
-        <v>14.74834299087524</v>
+        <v>16.52583861351013</v>
       </c>
       <c r="D40" t="n">
-        <v>16.68328762054443</v>
+        <v>13.42927622795105</v>
       </c>
       <c r="E40" t="n">
-        <v>14.07285618782043</v>
+        <v>13.02939105033875</v>
       </c>
       <c r="F40" t="n">
-        <v>13.98377442359924</v>
+        <v>20.62232398986816</v>
       </c>
       <c r="G40" t="n">
-        <v>12.72060751914978</v>
+        <v>14.67330074310303</v>
       </c>
       <c r="H40" t="n">
-        <v>16.76513338088989</v>
+        <v>15.46670031547546</v>
       </c>
       <c r="I40" t="n">
-        <v>12.85102963447571</v>
+        <v>13.90784621238708</v>
       </c>
       <c r="J40" t="n">
-        <v>18.16873574256897</v>
+        <v>13.61160111427307</v>
       </c>
       <c r="K40" t="n">
-        <v>15.76976752281189</v>
+        <v>13.13443851470947</v>
       </c>
       <c r="L40" t="n">
-        <v>15.18916230201721</v>
+        <v>14.92154936790466</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>16.48907446861267</v>
+        <v>14.87355780601501</v>
       </c>
       <c r="C41" t="n">
-        <v>15.18543648719788</v>
+        <v>10.57172799110413</v>
       </c>
       <c r="D41" t="n">
-        <v>11.38484001159668</v>
+        <v>10.92833542823792</v>
       </c>
       <c r="E41" t="n">
-        <v>14.38463497161865</v>
+        <v>15.57570672035217</v>
       </c>
       <c r="F41" t="n">
-        <v>12.28853988647461</v>
+        <v>15.10959386825562</v>
       </c>
       <c r="G41" t="n">
-        <v>13.23922801017761</v>
+        <v>14.67472577095032</v>
       </c>
       <c r="H41" t="n">
-        <v>10.57797241210938</v>
+        <v>11.28845977783203</v>
       </c>
       <c r="I41" t="n">
-        <v>15.61777591705322</v>
+        <v>14.21208715438843</v>
       </c>
       <c r="J41" t="n">
-        <v>14.02531957626343</v>
+        <v>13.6621618270874</v>
       </c>
       <c r="K41" t="n">
-        <v>16.11229157447815</v>
+        <v>12.31510376930237</v>
       </c>
       <c r="L41" t="n">
-        <v>13.93051133155823</v>
+        <v>13.32114601135254</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>13.38615798950195</v>
+        <v>16.85791826248169</v>
       </c>
       <c r="C42" t="n">
-        <v>16.63660860061646</v>
+        <v>12.5223650932312</v>
       </c>
       <c r="D42" t="n">
-        <v>12.46874976158142</v>
+        <v>14.8686683177948</v>
       </c>
       <c r="E42" t="n">
-        <v>17.45171713829041</v>
+        <v>17.56306290626526</v>
       </c>
       <c r="F42" t="n">
-        <v>15.94165921211243</v>
+        <v>13.86200404167175</v>
       </c>
       <c r="G42" t="n">
-        <v>12.99842619895935</v>
+        <v>13.25918340682983</v>
       </c>
       <c r="H42" t="n">
-        <v>15.19734048843384</v>
+        <v>12.42319416999817</v>
       </c>
       <c r="I42" t="n">
-        <v>14.28449535369873</v>
+        <v>14.04148244857788</v>
       </c>
       <c r="J42" t="n">
-        <v>14.07643985748291</v>
+        <v>15.16028833389282</v>
       </c>
       <c r="K42" t="n">
-        <v>13.02308082580566</v>
+        <v>14.70023369789124</v>
       </c>
       <c r="L42" t="n">
-        <v>14.54646754264832</v>
+        <v>14.52584006786346</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>11.30973649024963</v>
+        <v>12.83192229270935</v>
       </c>
       <c r="C43" t="n">
-        <v>13.51667618751526</v>
+        <v>17.79764318466187</v>
       </c>
       <c r="D43" t="n">
-        <v>14.52985191345215</v>
+        <v>12.12681531906128</v>
       </c>
       <c r="E43" t="n">
-        <v>12.61578774452209</v>
+        <v>12.55918550491333</v>
       </c>
       <c r="F43" t="n">
-        <v>15.38991236686707</v>
+        <v>14.15913510322571</v>
       </c>
       <c r="G43" t="n">
-        <v>12.76296257972717</v>
+        <v>17.85383462905884</v>
       </c>
       <c r="H43" t="n">
-        <v>19.99148201942444</v>
+        <v>14.72079348564148</v>
       </c>
       <c r="I43" t="n">
-        <v>15.8759458065033</v>
+        <v>14.7859091758728</v>
       </c>
       <c r="J43" t="n">
-        <v>17.93286108970642</v>
+        <v>13.30771398544312</v>
       </c>
       <c r="K43" t="n">
-        <v>16.27708911895752</v>
+        <v>14.41562032699585</v>
       </c>
       <c r="L43" t="n">
-        <v>15.0202305316925</v>
+        <v>14.45585730075836</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>19.06391906738281</v>
+        <v>18.13675975799561</v>
       </c>
       <c r="C44" t="n">
-        <v>19.1659300327301</v>
+        <v>18.00021409988403</v>
       </c>
       <c r="D44" t="n">
-        <v>14.4348566532135</v>
+        <v>21.81475186347961</v>
       </c>
       <c r="E44" t="n">
-        <v>15.47383618354797</v>
+        <v>17.16135907173157</v>
       </c>
       <c r="F44" t="n">
-        <v>14.62532520294189</v>
+        <v>15.43994140625</v>
       </c>
       <c r="G44" t="n">
-        <v>14.6285092830658</v>
+        <v>13.1809778213501</v>
       </c>
       <c r="H44" t="n">
-        <v>16.79480314254761</v>
+        <v>17.04579973220825</v>
       </c>
       <c r="I44" t="n">
-        <v>15.38603162765503</v>
+        <v>20.07564401626587</v>
       </c>
       <c r="J44" t="n">
-        <v>16.7335684299469</v>
+        <v>16.70474863052368</v>
       </c>
       <c r="K44" t="n">
-        <v>15.18446850776672</v>
+        <v>17.80783605575562</v>
       </c>
       <c r="L44" t="n">
-        <v>16.14912481307983</v>
+        <v>17.53680324554443</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>13.12202906608582</v>
+        <v>15.3768789768219</v>
       </c>
       <c r="C45" t="n">
-        <v>13.6209864616394</v>
+        <v>12.49950075149536</v>
       </c>
       <c r="D45" t="n">
-        <v>11.94332194328308</v>
+        <v>11.08792471885681</v>
       </c>
       <c r="E45" t="n">
-        <v>12.37930178642273</v>
+        <v>13.24408173561096</v>
       </c>
       <c r="F45" t="n">
-        <v>12.57205152511597</v>
+        <v>10.31744575500488</v>
       </c>
       <c r="G45" t="n">
-        <v>14.34193325042725</v>
+        <v>11.26786708831787</v>
       </c>
       <c r="H45" t="n">
-        <v>11.8068733215332</v>
+        <v>15.80457806587219</v>
       </c>
       <c r="I45" t="n">
-        <v>12.034264087677</v>
+        <v>14.46259164810181</v>
       </c>
       <c r="J45" t="n">
-        <v>14.36743974685669</v>
+        <v>10.84699249267578</v>
       </c>
       <c r="K45" t="n">
-        <v>12.10597896575928</v>
+        <v>14.03886675834656</v>
       </c>
       <c r="L45" t="n">
-        <v>12.82941801548004</v>
+        <v>12.89467279911041</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>19.19407653808594</v>
+        <v>16.50982737541199</v>
       </c>
       <c r="C46" t="n">
-        <v>20.82965087890625</v>
+        <v>17.6039891242981</v>
       </c>
       <c r="D46" t="n">
-        <v>16.52254605293274</v>
+        <v>16.11428713798523</v>
       </c>
       <c r="E46" t="n">
-        <v>18.03688621520996</v>
+        <v>14.23790907859802</v>
       </c>
       <c r="F46" t="n">
-        <v>13.94245982170105</v>
+        <v>17.57786107063293</v>
       </c>
       <c r="G46" t="n">
-        <v>14.02450013160706</v>
+        <v>20.31859016418457</v>
       </c>
       <c r="H46" t="n">
-        <v>18.00239396095276</v>
+        <v>16.36612033843994</v>
       </c>
       <c r="I46" t="n">
-        <v>16.740877866745</v>
+        <v>14.50969076156616</v>
       </c>
       <c r="J46" t="n">
-        <v>13.04984617233276</v>
+        <v>17.83312630653381</v>
       </c>
       <c r="K46" t="n">
-        <v>18.66020822525024</v>
+        <v>15.74184346199036</v>
       </c>
       <c r="L46" t="n">
-        <v>16.90034458637238</v>
+        <v>16.68132448196411</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>14.99415016174316</v>
+        <v>15.4153573513031</v>
       </c>
       <c r="C47" t="n">
-        <v>14.87839984893799</v>
+        <v>12.57712244987488</v>
       </c>
       <c r="D47" t="n">
-        <v>14.01260495185852</v>
+        <v>19.3718569278717</v>
       </c>
       <c r="E47" t="n">
-        <v>15.59616708755493</v>
+        <v>15.64592981338501</v>
       </c>
       <c r="F47" t="n">
-        <v>15.63620591163635</v>
+        <v>17.47023391723633</v>
       </c>
       <c r="G47" t="n">
-        <v>15.61628818511963</v>
+        <v>12.20340847969055</v>
       </c>
       <c r="H47" t="n">
-        <v>14.07372665405273</v>
+        <v>17.64193367958069</v>
       </c>
       <c r="I47" t="n">
-        <v>18.90098309516907</v>
+        <v>12.90259289741516</v>
       </c>
       <c r="J47" t="n">
-        <v>15.52446913719177</v>
+        <v>15.35725545883179</v>
       </c>
       <c r="K47" t="n">
-        <v>13.76513242721558</v>
+        <v>16.96856069564819</v>
       </c>
       <c r="L47" t="n">
-        <v>15.29981274604797</v>
+        <v>15.55542516708374</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>13.53427863121033</v>
+        <v>15.44606971740723</v>
       </c>
       <c r="C48" t="n">
-        <v>23.09227466583252</v>
+        <v>16.16491913795471</v>
       </c>
       <c r="D48" t="n">
-        <v>14.08106851577759</v>
+        <v>12.78321146965027</v>
       </c>
       <c r="E48" t="n">
-        <v>17.8163857460022</v>
+        <v>13.29060649871826</v>
       </c>
       <c r="F48" t="n">
-        <v>16.92485022544861</v>
+        <v>13.02417063713074</v>
       </c>
       <c r="G48" t="n">
-        <v>15.33920216560364</v>
+        <v>15.94689464569092</v>
       </c>
       <c r="H48" t="n">
-        <v>16.58480000495911</v>
+        <v>14.44977831840515</v>
       </c>
       <c r="I48" t="n">
-        <v>14.74714589118958</v>
+        <v>16.27901887893677</v>
       </c>
       <c r="J48" t="n">
-        <v>16.18284249305725</v>
+        <v>15.00022602081299</v>
       </c>
       <c r="K48" t="n">
-        <v>14.49241232872009</v>
+        <v>15.60397624969482</v>
       </c>
       <c r="L48" t="n">
-        <v>16.27952606678009</v>
+        <v>14.79888715744019</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>13.18076682090759</v>
+        <v>11.96224355697632</v>
       </c>
       <c r="C49" t="n">
-        <v>13.52249026298523</v>
+        <v>12.89665079116821</v>
       </c>
       <c r="D49" t="n">
-        <v>18.04549312591553</v>
+        <v>17.11327505111694</v>
       </c>
       <c r="E49" t="n">
-        <v>13.66891694068909</v>
+        <v>15.74841046333313</v>
       </c>
       <c r="F49" t="n">
-        <v>17.01932144165039</v>
+        <v>14.54917931556702</v>
       </c>
       <c r="G49" t="n">
-        <v>18.96278285980225</v>
+        <v>15.44375705718994</v>
       </c>
       <c r="H49" t="n">
-        <v>12.62825107574463</v>
+        <v>12.87058138847351</v>
       </c>
       <c r="I49" t="n">
-        <v>13.0753870010376</v>
+        <v>16.32833480834961</v>
       </c>
       <c r="J49" t="n">
-        <v>16.09669733047485</v>
+        <v>16.39415812492371</v>
       </c>
       <c r="K49" t="n">
-        <v>13.74842023849487</v>
+        <v>12.39884281158447</v>
       </c>
       <c r="L49" t="n">
-        <v>14.9948527097702</v>
+        <v>14.57054333686829</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>17.30660963058472</v>
+        <v>12.47880029678345</v>
       </c>
       <c r="C50" t="n">
-        <v>14.75821089744568</v>
+        <v>15.5446195602417</v>
       </c>
       <c r="D50" t="n">
-        <v>12.1161744594574</v>
+        <v>12.10567045211792</v>
       </c>
       <c r="E50" t="n">
-        <v>13.58044362068176</v>
+        <v>11.773108959198</v>
       </c>
       <c r="F50" t="n">
-        <v>15.71301484107971</v>
+        <v>12.77927684783936</v>
       </c>
       <c r="G50" t="n">
-        <v>12.66756653785706</v>
+        <v>11.99097323417664</v>
       </c>
       <c r="H50" t="n">
-        <v>13.32531046867371</v>
+        <v>16.7913293838501</v>
       </c>
       <c r="I50" t="n">
-        <v>13.82103967666626</v>
+        <v>15.6431667804718</v>
       </c>
       <c r="J50" t="n">
-        <v>12.65468001365662</v>
+        <v>14.75175809860229</v>
       </c>
       <c r="K50" t="n">
-        <v>14.28162598609924</v>
+        <v>12.69896245002747</v>
       </c>
       <c r="L50" t="n">
-        <v>14.02246761322021</v>
+        <v>13.65576660633087</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>12.71001791954041</v>
+        <v>11.77398610115051</v>
       </c>
       <c r="C51" t="n">
-        <v>10.54296684265137</v>
+        <v>12.74591517448425</v>
       </c>
       <c r="D51" t="n">
-        <v>13.31288576126099</v>
+        <v>14.28072214126587</v>
       </c>
       <c r="E51" t="n">
-        <v>12.41083455085754</v>
+        <v>13.18656992912292</v>
       </c>
       <c r="F51" t="n">
-        <v>11.59750127792358</v>
+        <v>12.09266138076782</v>
       </c>
       <c r="G51" t="n">
-        <v>12.48301649093628</v>
+        <v>11.97856307029724</v>
       </c>
       <c r="H51" t="n">
-        <v>11.48413252830505</v>
+        <v>12.75090217590332</v>
       </c>
       <c r="I51" t="n">
-        <v>11.45263504981995</v>
+        <v>12.65515756607056</v>
       </c>
       <c r="J51" t="n">
-        <v>13.08503770828247</v>
+        <v>11.51520562171936</v>
       </c>
       <c r="K51" t="n">
-        <v>14.22017860412598</v>
+        <v>11.47842144966125</v>
       </c>
       <c r="L51" t="n">
-        <v>12.32992067337036</v>
+        <v>12.44581046104431</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14.27586120128632</v>
+        <v>14.41960806369782</v>
       </c>
       <c r="C52" t="n">
-        <v>14.45214813709259</v>
+        <v>14.36410512924194</v>
       </c>
       <c r="D52" t="n">
-        <v>14.41254954338074</v>
+        <v>14.32418809890747</v>
       </c>
       <c r="E52" t="n">
-        <v>14.46610270023346</v>
+        <v>14.07563514709473</v>
       </c>
       <c r="F52" t="n">
-        <v>14.62288904190063</v>
+        <v>14.32511803150177</v>
       </c>
       <c r="G52" t="n">
-        <v>13.80617537975311</v>
+        <v>14.50316191673279</v>
       </c>
       <c r="H52" t="n">
-        <v>14.54713750362396</v>
+        <v>14.53592274665833</v>
       </c>
       <c r="I52" t="n">
-        <v>14.35931442260742</v>
+        <v>13.85861477851868</v>
       </c>
       <c r="J52" t="n">
-        <v>14.07330338001251</v>
+        <v>14.28268395900726</v>
       </c>
       <c r="K52" t="n">
-        <v>14.3190273475647</v>
+        <v>14.43821962833405</v>
       </c>
       <c r="L52" t="n">
-        <v>14.33345086574554</v>
+        <v>14.31272574996948</v>
       </c>
     </row>
   </sheetData>
